--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-27).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-27).xlsx
@@ -935,43 +935,43 @@
     <t>214</t>
   </si>
   <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>R$ 9.645,46</t>
-  </si>
-  <si>
-    <t>104.9</t>
-  </si>
-  <si>
-    <t>68.6</t>
-  </si>
-  <si>
-    <t>7.36</t>
-  </si>
-  <si>
-    <t>22.3</t>
-  </si>
-  <si>
-    <t>8.2</t>
-  </si>
-  <si>
-    <t>4.7</t>
-  </si>
-  <si>
-    <t>31.7%</t>
-  </si>
-  <si>
-    <t>16.5%</t>
-  </si>
-  <si>
-    <t>1.2%</t>
+    <t>33</t>
+  </si>
+  <si>
+    <t>R$ 9.451,70</t>
+  </si>
+  <si>
+    <t>101.1</t>
+  </si>
+  <si>
+    <t>66.0</t>
+  </si>
+  <si>
+    <t>7.46</t>
+  </si>
+  <si>
+    <t>22.9</t>
+  </si>
+  <si>
+    <t>8.7</t>
+  </si>
+  <si>
+    <t>6.0</t>
+  </si>
+  <si>
+    <t>29.5%</t>
+  </si>
+  <si>
+    <t>17.8%</t>
+  </si>
+  <si>
+    <t>1.3%</t>
   </si>
   <si>
     <t>0.4%</t>
   </si>
   <si>
-    <t>2.7%</t>
+    <t>3.0%</t>
   </si>
   <si>
     <t>0.9%</t>
@@ -980,49 +980,49 @@
     <t>0.1%</t>
   </si>
   <si>
-    <t>6.1%</t>
-  </si>
-  <si>
-    <t>2.5%</t>
-  </si>
-  <si>
-    <t>5.5%</t>
-  </si>
-  <si>
-    <t>1898.0</t>
-  </si>
-  <si>
-    <t>1583.0</t>
-  </si>
-  <si>
-    <t>114.0</t>
-  </si>
-  <si>
-    <t>35.0</t>
-  </si>
-  <si>
-    <t>260.0</t>
-  </si>
-  <si>
-    <t>86.0</t>
-  </si>
-  <si>
-    <t>14.0</t>
-  </si>
-  <si>
-    <t>583.0</t>
-  </si>
-  <si>
-    <t>243.0</t>
-  </si>
-  <si>
-    <t>528.0</t>
+    <t>5.8%</t>
+  </si>
+  <si>
+    <t>2.8%</t>
+  </si>
+  <si>
+    <t>6.3%</t>
+  </si>
+  <si>
+    <t>2448.0</t>
+  </si>
+  <si>
+    <t>2073.0</t>
+  </si>
+  <si>
+    <t>148.0</t>
+  </si>
+  <si>
+    <t>42.0</t>
+  </si>
+  <si>
+    <t>356.0</t>
+  </si>
+  <si>
+    <t>103.0</t>
+  </si>
+  <si>
+    <t>15.0</t>
+  </si>
+  <si>
+    <t>678.0</t>
+  </si>
+  <si>
+    <t>325.0</t>
+  </si>
+  <si>
+    <t>740.0</t>
   </si>
   <si>
     <t>0.7%</t>
   </si>
   <si>
-    <t>70.0</t>
+    <t>83.0</t>
   </si>
   <si>
     <t>1</t>
@@ -2115,7 +2115,7 @@
         <v>0.02564102564102564</v>
       </c>
       <c r="W5" s="9">
-        <v>0</v>
+        <v>0.012820512819999999</v>
       </c>
       <c r="X5" s="9">
         <v>0.01282051282051282</v>
@@ -2145,7 +2145,7 @@
         <v>2</v>
       </c>
       <c r="AG5" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH5" s="6">
         <v>1</v>
@@ -2928,7 +2928,7 @@
         <v>19513</v>
       </c>
       <c r="B11" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C11" s="4">
         <v>51</v>
@@ -2958,35 +2958,93 @@
         <v>58</v>
       </c>
       <c r="L11" s="4"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="8"/>
-      <c r="S11" s="8"/>
-      <c r="T11" s="9"/>
-      <c r="U11" s="9"/>
-      <c r="V11" s="9"/>
-      <c r="W11" s="9"/>
-      <c r="X11" s="9"/>
-      <c r="Y11" s="9"/>
-      <c r="Z11" s="9"/>
-      <c r="AA11" s="9"/>
-      <c r="AB11" s="9"/>
-      <c r="AC11" s="9"/>
-      <c r="AD11" s="6"/>
-      <c r="AE11" s="6"/>
-      <c r="AF11" s="6"/>
-      <c r="AG11" s="6"/>
-      <c r="AH11" s="6"/>
-      <c r="AI11" s="6"/>
-      <c r="AJ11" s="6"/>
-      <c r="AK11" s="6"/>
-      <c r="AL11" s="6"/>
-      <c r="AM11" s="6"/>
-      <c r="AN11" s="9"/>
-      <c r="AO11" s="6"/>
+      <c r="M11" s="5">
+        <v>13595.43</v>
+      </c>
+      <c r="N11" s="6">
+        <v>138</v>
+      </c>
+      <c r="O11" s="6">
+        <v>103</v>
+      </c>
+      <c r="P11" s="7">
+        <v>5.2731417266187046</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>16.193041747572813</v>
+      </c>
+      <c r="R11" s="8">
+        <v>4.9498346534653459</v>
+      </c>
+      <c r="S11" s="8">
+        <v>6</v>
+      </c>
+      <c r="T11" s="9">
+        <v>0.44660194174757284</v>
+      </c>
+      <c r="U11" s="9">
+        <v>0.1553398058252427</v>
+      </c>
+      <c r="V11" s="9">
+        <v>0</v>
+      </c>
+      <c r="W11" s="9">
+        <v>0</v>
+      </c>
+      <c r="X11" s="9">
+        <v>0.0097087378640776691</v>
+      </c>
+      <c r="Y11" s="9">
+        <v>0.0097087378640776691</v>
+      </c>
+      <c r="Z11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="9">
+        <v>0.019417475728155338</v>
+      </c>
+      <c r="AB11" s="9">
+        <v>0.0097087378640776691</v>
+      </c>
+      <c r="AC11" s="9">
+        <v>0.11650485436893204</v>
+      </c>
+      <c r="AD11" s="6">
+        <v>18</v>
+      </c>
+      <c r="AE11" s="6">
+        <v>16</v>
+      </c>
+      <c r="AF11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI11" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL11" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM11" s="6">
+        <v>12</v>
+      </c>
+      <c r="AN11" s="9">
+        <v>0.0097087378640776691</v>
+      </c>
+      <c r="AO11" s="6">
+        <v>1</v>
+      </c>
       <c t="s" r="AP11" s="4">
         <v>58</v>
       </c>
@@ -3184,7 +3242,7 @@
         <v>19515</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C13" s="4">
         <v>51</v>
@@ -3214,35 +3272,93 @@
         <v>58</v>
       </c>
       <c r="L13" s="4"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
-      <c r="T13" s="9"/>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="9"/>
-      <c r="Z13" s="9"/>
-      <c r="AA13" s="9"/>
-      <c r="AB13" s="9"/>
-      <c r="AC13" s="9"/>
-      <c r="AD13" s="6"/>
-      <c r="AE13" s="6"/>
-      <c r="AF13" s="6"/>
-      <c r="AG13" s="6"/>
-      <c r="AH13" s="6"/>
-      <c r="AI13" s="6"/>
-      <c r="AJ13" s="6"/>
-      <c r="AK13" s="6"/>
-      <c r="AL13" s="6"/>
-      <c r="AM13" s="6"/>
-      <c r="AN13" s="9"/>
-      <c r="AO13" s="6"/>
+      <c r="M13" s="5">
+        <v>17216.869999999999</v>
+      </c>
+      <c r="N13" s="6">
+        <v>181</v>
+      </c>
+      <c r="O13" s="6">
+        <v>127</v>
+      </c>
+      <c r="P13" s="7">
+        <v>7.4502762430939224</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>25.27178503937008</v>
+      </c>
+      <c r="R13" s="8">
+        <v>10.281496062992126</v>
+      </c>
+      <c r="S13" s="8">
+        <v>7</v>
+      </c>
+      <c r="T13" s="9">
+        <v>0.062992125984251968</v>
+      </c>
+      <c r="U13" s="9">
+        <v>0.22047244094488189</v>
+      </c>
+      <c r="V13" s="9">
+        <v>0.007874015748031496</v>
+      </c>
+      <c r="W13" s="9">
+        <v>0</v>
+      </c>
+      <c r="X13" s="9">
+        <v>0.023622047244094488</v>
+      </c>
+      <c r="Y13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="9">
+        <v>0.1889763779527559</v>
+      </c>
+      <c r="AD13" s="6">
+        <v>28</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>28</v>
+      </c>
+      <c r="AF13" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="6">
+        <v>24</v>
+      </c>
+      <c r="AN13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP13" s="4">
         <v>58</v>
       </c>
@@ -3748,7 +3864,7 @@
         <v>19521</v>
       </c>
       <c r="B17" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C17" s="4">
         <v>51</v>
@@ -3778,8 +3894,12 @@
         <v>58</v>
       </c>
       <c r="L17" s="4"/>
-      <c r="M17" s="5"/>
-      <c r="N17" s="6"/>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="6">
+        <v>0</v>
+      </c>
       <c r="O17" s="6"/>
       <c r="P17" s="7"/>
       <c r="Q17" s="8"/>
@@ -5043,7 +5163,7 @@
         <v>19540</v>
       </c>
       <c r="B26" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C26" s="4">
         <v>51</v>
@@ -5073,35 +5193,93 @@
         <v>58</v>
       </c>
       <c r="L26" s="4"/>
-      <c r="M26" s="5"/>
-      <c r="N26" s="6"/>
-      <c r="O26" s="6"/>
-      <c r="P26" s="7"/>
-      <c r="Q26" s="8"/>
-      <c r="R26" s="8"/>
-      <c r="S26" s="8"/>
-      <c r="T26" s="9"/>
-      <c r="U26" s="9"/>
-      <c r="V26" s="9"/>
-      <c r="W26" s="9"/>
-      <c r="X26" s="9"/>
-      <c r="Y26" s="9"/>
-      <c r="Z26" s="9"/>
-      <c r="AA26" s="9"/>
-      <c r="AB26" s="9"/>
-      <c r="AC26" s="9"/>
-      <c r="AD26" s="6"/>
-      <c r="AE26" s="6"/>
-      <c r="AF26" s="6"/>
-      <c r="AG26" s="6"/>
-      <c r="AH26" s="6"/>
-      <c r="AI26" s="6"/>
-      <c r="AJ26" s="6"/>
-      <c r="AK26" s="6"/>
-      <c r="AL26" s="6"/>
-      <c r="AM26" s="6"/>
-      <c r="AN26" s="9"/>
-      <c r="AO26" s="6"/>
+      <c r="M26" s="5">
+        <v>14067.030000000001</v>
+      </c>
+      <c r="N26" s="6">
+        <v>143</v>
+      </c>
+      <c r="O26" s="6">
+        <v>101</v>
+      </c>
+      <c r="P26" s="7">
+        <v>2.8036613636363636</v>
+      </c>
+      <c r="Q26" s="8">
+        <v>18.571121782178217</v>
+      </c>
+      <c r="R26" s="8">
+        <v>9.6788197916666672</v>
+      </c>
+      <c r="S26" s="8">
+        <v>7</v>
+      </c>
+      <c r="T26" s="9">
+        <v>0.34653465346534651</v>
+      </c>
+      <c r="U26" s="9">
+        <v>0.26732673267326734</v>
+      </c>
+      <c r="V26" s="9">
+        <v>0.0099009900990099011</v>
+      </c>
+      <c r="W26" s="9">
+        <v>0.0099009900989999993</v>
+      </c>
+      <c r="X26" s="9">
+        <v>0.22772277227722773</v>
+      </c>
+      <c r="Y26" s="9">
+        <v>0.039603960396039604</v>
+      </c>
+      <c r="Z26" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="9">
+        <v>0.049504950495049507</v>
+      </c>
+      <c r="AB26" s="9">
+        <v>0.0099009900990099011</v>
+      </c>
+      <c r="AC26" s="9">
+        <v>0.019801980198019802</v>
+      </c>
+      <c r="AD26" s="6">
+        <v>37</v>
+      </c>
+      <c r="AE26" s="6">
+        <v>27</v>
+      </c>
+      <c r="AF26" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG26" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH26" s="6">
+        <v>23</v>
+      </c>
+      <c r="AI26" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ26" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL26" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM26" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN26" s="9">
+        <v>0.0099009900990099011</v>
+      </c>
+      <c r="AO26" s="6">
+        <v>1</v>
+      </c>
       <c t="s" r="AP26" s="4">
         <v>58</v>
       </c>
@@ -5142,7 +5320,7 @@
         <v>19545</v>
       </c>
       <c r="B27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C27" s="4">
         <v>51</v>
@@ -5172,35 +5350,93 @@
         <v>58</v>
       </c>
       <c r="L27" s="4"/>
-      <c r="M27" s="5"/>
-      <c r="N27" s="6"/>
-      <c r="O27" s="6"/>
-      <c r="P27" s="7"/>
-      <c r="Q27" s="8"/>
-      <c r="R27" s="8"/>
-      <c r="S27" s="8"/>
-      <c r="T27" s="9"/>
-      <c r="U27" s="9"/>
-      <c r="V27" s="9"/>
-      <c r="W27" s="9"/>
-      <c r="X27" s="9"/>
-      <c r="Y27" s="9"/>
-      <c r="Z27" s="9"/>
-      <c r="AA27" s="9"/>
-      <c r="AB27" s="9"/>
-      <c r="AC27" s="9"/>
-      <c r="AD27" s="6"/>
-      <c r="AE27" s="6"/>
-      <c r="AF27" s="6"/>
-      <c r="AG27" s="6"/>
-      <c r="AH27" s="6"/>
-      <c r="AI27" s="6"/>
-      <c r="AJ27" s="6"/>
-      <c r="AK27" s="6"/>
-      <c r="AL27" s="6"/>
-      <c r="AM27" s="6"/>
-      <c r="AN27" s="9"/>
-      <c r="AO27" s="6"/>
+      <c r="M27" s="5">
+        <v>6869.5500000000002</v>
+      </c>
+      <c r="N27" s="6">
+        <v>71</v>
+      </c>
+      <c r="O27" s="6">
+        <v>41</v>
+      </c>
+      <c r="P27" s="7">
+        <v>4.8387323943661977</v>
+      </c>
+      <c r="Q27" s="8">
+        <v>21.140243902439025</v>
+      </c>
+      <c r="R27" s="8">
+        <v>7.9700000000000006</v>
+      </c>
+      <c r="S27" s="8">
+        <v>8</v>
+      </c>
+      <c r="T27" s="9">
+        <v>0.34146341463414637</v>
+      </c>
+      <c r="U27" s="9">
+        <v>0.21951219512195122</v>
+      </c>
+      <c r="V27" s="9">
+        <v>0.073170731707317069</v>
+      </c>
+      <c r="W27" s="9">
+        <v>0</v>
+      </c>
+      <c r="X27" s="9">
+        <v>0.073170731707317069</v>
+      </c>
+      <c r="Y27" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="9">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="AB27" s="9">
+        <v>0.024390243902439025</v>
+      </c>
+      <c r="AC27" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="6">
+        <v>9</v>
+      </c>
+      <c r="AE27" s="6">
+        <v>9</v>
+      </c>
+      <c r="AF27" s="6">
+        <v>3</v>
+      </c>
+      <c r="AG27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK27" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL27" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN27" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO27" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP27" s="4">
         <v>58</v>
       </c>
@@ -5241,7 +5477,7 @@
         <v>19546</v>
       </c>
       <c r="B28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C28" s="4">
         <v>51</v>
@@ -5271,35 +5507,93 @@
         <v>58</v>
       </c>
       <c r="L28" s="4"/>
-      <c r="M28" s="5"/>
-      <c r="N28" s="6"/>
-      <c r="O28" s="6"/>
-      <c r="P28" s="7"/>
-      <c r="Q28" s="8"/>
-      <c r="R28" s="8"/>
-      <c r="S28" s="8"/>
-      <c r="T28" s="9"/>
-      <c r="U28" s="9"/>
-      <c r="V28" s="9"/>
-      <c r="W28" s="9"/>
-      <c r="X28" s="9"/>
-      <c r="Y28" s="9"/>
-      <c r="Z28" s="9"/>
-      <c r="AA28" s="9"/>
-      <c r="AB28" s="9"/>
-      <c r="AC28" s="9"/>
-      <c r="AD28" s="6"/>
-      <c r="AE28" s="6"/>
-      <c r="AF28" s="6"/>
-      <c r="AG28" s="6"/>
-      <c r="AH28" s="6"/>
-      <c r="AI28" s="6"/>
-      <c r="AJ28" s="6"/>
-      <c r="AK28" s="6"/>
-      <c r="AL28" s="6"/>
-      <c r="AM28" s="6"/>
-      <c r="AN28" s="9"/>
-      <c r="AO28" s="6"/>
+      <c r="M28" s="5">
+        <v>8211.7700000000004</v>
+      </c>
+      <c r="N28" s="6">
+        <v>89</v>
+      </c>
+      <c r="O28" s="6">
+        <v>55</v>
+      </c>
+      <c r="P28" s="7">
+        <v>2.448467816091954</v>
+      </c>
+      <c r="Q28" s="8">
+        <v>17.478787272727274</v>
+      </c>
+      <c r="R28" s="8">
+        <v>7.9930309090909084</v>
+      </c>
+      <c r="S28" s="8">
+        <v>7</v>
+      </c>
+      <c r="T28" s="9">
+        <v>0.38181818181818183</v>
+      </c>
+      <c r="U28" s="9">
+        <v>0.23636363636363636</v>
+      </c>
+      <c r="V28" s="9">
+        <v>0</v>
+      </c>
+      <c r="W28" s="9">
+        <v>0</v>
+      </c>
+      <c r="X28" s="9">
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="Y28" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="9">
+        <v>0.018181818181818181</v>
+      </c>
+      <c r="AB28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="9">
+        <v>0.072727272727272724</v>
+      </c>
+      <c r="AD28" s="6">
+        <v>15</v>
+      </c>
+      <c r="AE28" s="6">
+        <v>13</v>
+      </c>
+      <c r="AF28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="6">
+        <v>10</v>
+      </c>
+      <c r="AI28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP28" s="4">
         <v>58</v>
       </c>
@@ -5968,7 +6262,7 @@
         <v>19553</v>
       </c>
       <c r="B33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C33" s="4">
         <v>51</v>
@@ -5996,35 +6290,93 @@
         <v>58</v>
       </c>
       <c r="L33" s="4"/>
-      <c r="M33" s="5"/>
-      <c r="N33" s="6"/>
-      <c r="O33" s="6"/>
-      <c r="P33" s="7"/>
-      <c r="Q33" s="8"/>
-      <c r="R33" s="8"/>
-      <c r="S33" s="8"/>
-      <c r="T33" s="9"/>
-      <c r="U33" s="9"/>
-      <c r="V33" s="9"/>
-      <c r="W33" s="9"/>
-      <c r="X33" s="9"/>
-      <c r="Y33" s="9"/>
-      <c r="Z33" s="9"/>
-      <c r="AA33" s="9"/>
-      <c r="AB33" s="9"/>
-      <c r="AC33" s="9"/>
-      <c r="AD33" s="6"/>
-      <c r="AE33" s="6"/>
-      <c r="AF33" s="6"/>
-      <c r="AG33" s="6"/>
-      <c r="AH33" s="6"/>
-      <c r="AI33" s="6"/>
-      <c r="AJ33" s="6"/>
-      <c r="AK33" s="6"/>
-      <c r="AL33" s="6"/>
-      <c r="AM33" s="6"/>
-      <c r="AN33" s="9"/>
-      <c r="AO33" s="6"/>
+      <c r="M33" s="5">
+        <v>11712.450000000001</v>
+      </c>
+      <c r="N33" s="6">
+        <v>115</v>
+      </c>
+      <c r="O33" s="6">
+        <v>63</v>
+      </c>
+      <c r="P33" s="7">
+        <v>3.261304347826087</v>
+      </c>
+      <c r="Q33" s="8">
+        <v>19.255820634920635</v>
+      </c>
+      <c r="R33" s="8">
+        <v>9.1696241935483869</v>
+      </c>
+      <c r="S33" s="8">
+        <v>7</v>
+      </c>
+      <c r="T33" s="9">
+        <v>0.15873015873015872</v>
+      </c>
+      <c r="U33" s="9">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="V33" s="9">
+        <v>0.015873015873015872</v>
+      </c>
+      <c r="W33" s="9">
+        <v>0</v>
+      </c>
+      <c r="X33" s="9">
+        <v>0.047619047619047616</v>
+      </c>
+      <c r="Y33" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="9">
+        <v>0.015873015873015872</v>
+      </c>
+      <c r="AB33" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="6">
+        <v>8</v>
+      </c>
+      <c r="AE33" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF33" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG33" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI33" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ33" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK33" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL33" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM33" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN33" s="9">
+        <v>0.047619047619047616</v>
+      </c>
+      <c r="AO33" s="6">
+        <v>3</v>
+      </c>
       <c t="s" r="AP33" s="4">
         <v>58</v>
       </c>
@@ -6790,7 +7142,7 @@
         <v>19565</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C39" s="4">
         <v>51</v>
@@ -6820,35 +7172,93 @@
         <v>58</v>
       </c>
       <c r="L39" s="4"/>
-      <c r="M39" s="5"/>
-      <c r="N39" s="6"/>
-      <c r="O39" s="6"/>
-      <c r="P39" s="7"/>
-      <c r="Q39" s="8"/>
-      <c r="R39" s="8"/>
-      <c r="S39" s="8"/>
-      <c r="T39" s="9"/>
-      <c r="U39" s="9"/>
-      <c r="V39" s="9"/>
-      <c r="W39" s="9"/>
-      <c r="X39" s="9"/>
-      <c r="Y39" s="9"/>
-      <c r="Z39" s="9"/>
-      <c r="AA39" s="9"/>
-      <c r="AB39" s="9"/>
-      <c r="AC39" s="9"/>
-      <c r="AD39" s="6"/>
-      <c r="AE39" s="6"/>
-      <c r="AF39" s="6"/>
-      <c r="AG39" s="6"/>
-      <c r="AH39" s="6"/>
-      <c r="AI39" s="6"/>
-      <c r="AJ39" s="6"/>
-      <c r="AK39" s="6"/>
-      <c r="AL39" s="6"/>
-      <c r="AM39" s="6"/>
-      <c r="AN39" s="9"/>
-      <c r="AO39" s="6"/>
+      <c r="M39" s="5">
+        <v>16411.080000000002</v>
+      </c>
+      <c r="N39" s="6">
+        <v>179</v>
+      </c>
+      <c r="O39" s="6">
+        <v>129</v>
+      </c>
+      <c r="P39" s="7">
+        <v>4.543223626373627</v>
+      </c>
+      <c r="Q39" s="8">
+        <v>24.586328125000001</v>
+      </c>
+      <c r="R39" s="8">
+        <v>13.90940170940171</v>
+      </c>
+      <c r="S39" s="8">
+        <v>8</v>
+      </c>
+      <c r="T39" s="9">
+        <v>0.171875</v>
+      </c>
+      <c r="U39" s="9">
+        <v>0.17054263565891473</v>
+      </c>
+      <c r="V39" s="9">
+        <v>0.015503875968992248</v>
+      </c>
+      <c r="W39" s="9">
+        <v>0</v>
+      </c>
+      <c r="X39" s="9">
+        <v>0.03875968992248062</v>
+      </c>
+      <c r="Y39" s="9">
+        <v>0.054263565891472867</v>
+      </c>
+      <c r="Z39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="9">
+        <v>0.11627906976744186</v>
+      </c>
+      <c r="AB39" s="9">
+        <v>0.062015503875968991</v>
+      </c>
+      <c r="AC39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="6">
+        <v>37</v>
+      </c>
+      <c r="AE39" s="6">
+        <v>22</v>
+      </c>
+      <c r="AF39" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH39" s="6">
+        <v>5</v>
+      </c>
+      <c r="AI39" s="6">
+        <v>7</v>
+      </c>
+      <c r="AJ39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK39" s="6">
+        <v>15</v>
+      </c>
+      <c r="AL39" s="6">
+        <v>8</v>
+      </c>
+      <c r="AM39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO39" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP39" s="4">
         <v>58</v>
       </c>
@@ -7302,7 +7712,7 @@
         <v>19580</v>
       </c>
       <c r="B43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C43" s="4">
         <v>51</v>
@@ -7332,35 +7742,93 @@
         <v>58</v>
       </c>
       <c r="L43" s="4"/>
-      <c r="M43" s="5"/>
-      <c r="N43" s="6"/>
-      <c r="O43" s="6"/>
-      <c r="P43" s="7"/>
-      <c r="Q43" s="8"/>
-      <c r="R43" s="8"/>
-      <c r="S43" s="8"/>
-      <c r="T43" s="9"/>
-      <c r="U43" s="9"/>
-      <c r="V43" s="9"/>
-      <c r="W43" s="9"/>
-      <c r="X43" s="9"/>
-      <c r="Y43" s="9"/>
-      <c r="Z43" s="9"/>
-      <c r="AA43" s="9"/>
-      <c r="AB43" s="9"/>
-      <c r="AC43" s="9"/>
-      <c r="AD43" s="6"/>
-      <c r="AE43" s="6"/>
-      <c r="AF43" s="6"/>
-      <c r="AG43" s="6"/>
-      <c r="AH43" s="6"/>
-      <c r="AI43" s="6"/>
-      <c r="AJ43" s="6"/>
-      <c r="AK43" s="6"/>
-      <c r="AL43" s="6"/>
-      <c r="AM43" s="6"/>
-      <c r="AN43" s="9"/>
-      <c r="AO43" s="6"/>
+      <c r="M43" s="5">
+        <v>11930.93</v>
+      </c>
+      <c r="N43" s="6">
+        <v>118</v>
+      </c>
+      <c r="O43" s="6">
+        <v>84</v>
+      </c>
+      <c r="P43" s="7">
+        <v>7.7787353448275862</v>
+      </c>
+      <c r="Q43" s="8">
+        <v>23.610714285714284</v>
+      </c>
+      <c r="R43" s="8">
+        <v>9.3375531645569616</v>
+      </c>
+      <c r="S43" s="8">
+        <v>7</v>
+      </c>
+      <c r="T43" s="9">
+        <v>0.047619047619047616</v>
+      </c>
+      <c r="U43" s="9">
+        <v>0.11904761904761904</v>
+      </c>
+      <c r="V43" s="9">
+        <v>0</v>
+      </c>
+      <c r="W43" s="9">
+        <v>0</v>
+      </c>
+      <c r="X43" s="9">
+        <v>0.011904761904761904</v>
+      </c>
+      <c r="Y43" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="AB43" s="9">
+        <v>0.035714285714285712</v>
+      </c>
+      <c r="AC43" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="6">
+        <v>10</v>
+      </c>
+      <c r="AE43" s="6">
+        <v>10</v>
+      </c>
+      <c r="AF43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK43" s="6">
+        <v>6</v>
+      </c>
+      <c r="AL43" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN43" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO43" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP43" s="4">
         <v>58</v>
       </c>
@@ -8337,7 +8805,7 @@
         <v>19601</v>
       </c>
       <c r="B50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C50" s="4">
         <v>51</v>
@@ -8367,35 +8835,93 @@
         <v>58</v>
       </c>
       <c r="L50" s="4"/>
-      <c r="M50" s="5"/>
-      <c r="N50" s="6"/>
-      <c r="O50" s="6"/>
-      <c r="P50" s="7"/>
-      <c r="Q50" s="8"/>
-      <c r="R50" s="8"/>
-      <c r="S50" s="8"/>
-      <c r="T50" s="9"/>
-      <c r="U50" s="9"/>
-      <c r="V50" s="9"/>
-      <c r="W50" s="9"/>
-      <c r="X50" s="9"/>
-      <c r="Y50" s="9"/>
-      <c r="Z50" s="9"/>
-      <c r="AA50" s="9"/>
-      <c r="AB50" s="9"/>
-      <c r="AC50" s="9"/>
-      <c r="AD50" s="6"/>
-      <c r="AE50" s="6"/>
-      <c r="AF50" s="6"/>
-      <c r="AG50" s="6"/>
-      <c r="AH50" s="6"/>
-      <c r="AI50" s="6"/>
-      <c r="AJ50" s="6"/>
-      <c r="AK50" s="6"/>
-      <c r="AL50" s="6"/>
-      <c r="AM50" s="6"/>
-      <c r="AN50" s="9"/>
-      <c r="AO50" s="6"/>
+      <c r="M50" s="5">
+        <v>14984</v>
+      </c>
+      <c r="N50" s="6">
+        <v>172</v>
+      </c>
+      <c r="O50" s="6">
+        <v>105</v>
+      </c>
+      <c r="P50" s="7">
+        <v>3.3357701754385967</v>
+      </c>
+      <c r="Q50" s="8">
+        <v>19.948730476190477</v>
+      </c>
+      <c r="R50" s="8">
+        <v>8.7298409523809521</v>
+      </c>
+      <c r="S50" s="8">
+        <v>8</v>
+      </c>
+      <c r="T50" s="9">
+        <v>0.20952380952380953</v>
+      </c>
+      <c r="U50" s="9">
+        <v>0.35238095238095241</v>
+      </c>
+      <c r="V50" s="9">
+        <v>0.028571428571428571</v>
+      </c>
+      <c r="W50" s="9">
+        <v>0.0095238095230000003</v>
+      </c>
+      <c r="X50" s="9">
+        <v>0.038095238095238099</v>
+      </c>
+      <c r="Y50" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="9">
+        <v>0.0095238095238095247</v>
+      </c>
+      <c r="AB50" s="9">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AC50" s="9">
+        <v>0.038095238095238099</v>
+      </c>
+      <c r="AD50" s="6">
+        <v>42</v>
+      </c>
+      <c r="AE50" s="6">
+        <v>37</v>
+      </c>
+      <c r="AF50" s="6">
+        <v>3</v>
+      </c>
+      <c r="AG50" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH50" s="6">
+        <v>4</v>
+      </c>
+      <c r="AI50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL50" s="6">
+        <v>30</v>
+      </c>
+      <c r="AM50" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN50" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO50" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP50" s="4">
         <v>58</v>
       </c>
@@ -8847,7 +9373,7 @@
         <v>19609</v>
       </c>
       <c r="B54" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C54" s="4">
         <v>51</v>
@@ -8877,35 +9403,93 @@
         <v>58</v>
       </c>
       <c r="L54" s="4"/>
-      <c r="M54" s="5"/>
-      <c r="N54" s="6"/>
-      <c r="O54" s="6"/>
-      <c r="P54" s="7"/>
-      <c r="Q54" s="8"/>
-      <c r="R54" s="8"/>
-      <c r="S54" s="8"/>
-      <c r="T54" s="9"/>
-      <c r="U54" s="9"/>
-      <c r="V54" s="9"/>
-      <c r="W54" s="9"/>
-      <c r="X54" s="9"/>
-      <c r="Y54" s="9"/>
-      <c r="Z54" s="9"/>
-      <c r="AA54" s="9"/>
-      <c r="AB54" s="9"/>
-      <c r="AC54" s="9"/>
-      <c r="AD54" s="6"/>
-      <c r="AE54" s="6"/>
-      <c r="AF54" s="6"/>
-      <c r="AG54" s="6"/>
-      <c r="AH54" s="6"/>
-      <c r="AI54" s="6"/>
-      <c r="AJ54" s="6"/>
-      <c r="AK54" s="6"/>
-      <c r="AL54" s="6"/>
-      <c r="AM54" s="6"/>
-      <c r="AN54" s="9"/>
-      <c r="AO54" s="6"/>
+      <c r="M54" s="5">
+        <v>7974.0600000000004</v>
+      </c>
+      <c r="N54" s="6">
+        <v>86</v>
+      </c>
+      <c r="O54" s="6">
+        <v>58</v>
+      </c>
+      <c r="P54" s="7">
+        <v>6.94902</v>
+      </c>
+      <c r="Q54" s="8">
+        <v>21.449425862068967</v>
+      </c>
+      <c r="R54" s="8">
+        <v>7.5508620689655173</v>
+      </c>
+      <c r="S54" s="8">
+        <v>7</v>
+      </c>
+      <c r="T54" s="9">
+        <v>0.22413793103448276</v>
+      </c>
+      <c r="U54" s="9">
+        <v>0.13793103448275862</v>
+      </c>
+      <c r="V54" s="9">
+        <v>0.017241379310344827</v>
+      </c>
+      <c r="W54" s="9">
+        <v>0</v>
+      </c>
+      <c r="X54" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA54" s="9">
+        <v>0.017241379310344827</v>
+      </c>
+      <c r="AB54" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC54" s="9">
+        <v>0.10344827586206896</v>
+      </c>
+      <c r="AD54" s="6">
+        <v>8</v>
+      </c>
+      <c r="AE54" s="6">
+        <v>8</v>
+      </c>
+      <c r="AF54" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG54" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH54" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI54" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ54" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK54" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL54" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM54" s="6">
+        <v>6</v>
+      </c>
+      <c r="AN54" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO54" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP54" s="4">
         <v>58</v>
       </c>
@@ -8946,7 +9530,7 @@
         <v>19615</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>51</v>
@@ -8976,35 +9560,93 @@
         <v>58</v>
       </c>
       <c r="L55" s="4"/>
-      <c r="M55" s="5"/>
-      <c r="N55" s="6"/>
-      <c r="O55" s="6"/>
-      <c r="P55" s="7"/>
-      <c r="Q55" s="8"/>
-      <c r="R55" s="8"/>
-      <c r="S55" s="8"/>
-      <c r="T55" s="9"/>
-      <c r="U55" s="9"/>
-      <c r="V55" s="9"/>
-      <c r="W55" s="9"/>
-      <c r="X55" s="9"/>
-      <c r="Y55" s="9"/>
-      <c r="Z55" s="9"/>
-      <c r="AA55" s="9"/>
-      <c r="AB55" s="9"/>
-      <c r="AC55" s="9"/>
-      <c r="AD55" s="6"/>
-      <c r="AE55" s="6"/>
-      <c r="AF55" s="6"/>
-      <c r="AG55" s="6"/>
-      <c r="AH55" s="6"/>
-      <c r="AI55" s="6"/>
-      <c r="AJ55" s="6"/>
-      <c r="AK55" s="6"/>
-      <c r="AL55" s="6"/>
-      <c r="AM55" s="6"/>
-      <c r="AN55" s="9"/>
-      <c r="AO55" s="6"/>
+      <c r="M55" s="5">
+        <v>7889.4399999999996</v>
+      </c>
+      <c r="N55" s="6">
+        <v>99</v>
+      </c>
+      <c r="O55" s="6">
+        <v>73</v>
+      </c>
+      <c r="P55" s="7">
+        <v>8.6496702970297026</v>
+      </c>
+      <c r="Q55" s="8">
+        <v>39.52014925373134</v>
+      </c>
+      <c r="R55" s="8">
+        <v>24.322980303030306</v>
+      </c>
+      <c r="S55" s="8">
+        <v>7</v>
+      </c>
+      <c r="T55" s="9">
+        <v>0.014925373134328358</v>
+      </c>
+      <c r="U55" s="9">
+        <v>0.27397260273972601</v>
+      </c>
+      <c r="V55" s="9">
+        <v>0.013698630136986301</v>
+      </c>
+      <c r="W55" s="9">
+        <v>0</v>
+      </c>
+      <c r="X55" s="9">
+        <v>0.013698630136986301</v>
+      </c>
+      <c r="Y55" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="9">
+        <v>0.013698630136986301</v>
+      </c>
+      <c r="AB55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC55" s="9">
+        <v>0.23287671232876711</v>
+      </c>
+      <c r="AD55" s="6">
+        <v>20</v>
+      </c>
+      <c r="AE55" s="6">
+        <v>20</v>
+      </c>
+      <c r="AF55" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH55" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK55" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM55" s="6">
+        <v>17</v>
+      </c>
+      <c r="AN55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO55" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP55" s="4">
         <v>58</v>
       </c>
@@ -9613,7 +10255,7 @@
         <v>19623</v>
       </c>
       <c r="B60" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C60" s="4">
         <v>51</v>
@@ -9643,35 +10285,93 @@
         <v>58</v>
       </c>
       <c r="L60" s="4"/>
-      <c r="M60" s="5"/>
-      <c r="N60" s="6"/>
-      <c r="O60" s="6"/>
-      <c r="P60" s="7"/>
-      <c r="Q60" s="8"/>
-      <c r="R60" s="8"/>
-      <c r="S60" s="8"/>
-      <c r="T60" s="9"/>
-      <c r="U60" s="9"/>
-      <c r="V60" s="9"/>
-      <c r="W60" s="9"/>
-      <c r="X60" s="9"/>
-      <c r="Y60" s="9"/>
-      <c r="Z60" s="9"/>
-      <c r="AA60" s="9"/>
-      <c r="AB60" s="9"/>
-      <c r="AC60" s="9"/>
-      <c r="AD60" s="6"/>
-      <c r="AE60" s="6"/>
-      <c r="AF60" s="6"/>
-      <c r="AG60" s="6"/>
-      <c r="AH60" s="6"/>
-      <c r="AI60" s="6"/>
-      <c r="AJ60" s="6"/>
-      <c r="AK60" s="6"/>
-      <c r="AL60" s="6"/>
-      <c r="AM60" s="6"/>
-      <c r="AN60" s="9"/>
-      <c r="AO60" s="6"/>
+      <c r="M60" s="5">
+        <v>7797.1499999999996</v>
+      </c>
+      <c r="N60" s="6">
+        <v>92</v>
+      </c>
+      <c r="O60" s="6">
+        <v>55</v>
+      </c>
+      <c r="P60" s="7">
+        <v>5.3207411111111105</v>
+      </c>
+      <c r="Q60" s="8">
+        <v>16.621212727272727</v>
+      </c>
+      <c r="R60" s="8">
+        <v>3.7225314814814814</v>
+      </c>
+      <c r="S60" s="8">
+        <v>8</v>
+      </c>
+      <c r="T60" s="9">
+        <v>0.50909090909090904</v>
+      </c>
+      <c r="U60" s="9">
+        <v>0.21818181818181817</v>
+      </c>
+      <c r="V60" s="9">
+        <v>0</v>
+      </c>
+      <c r="W60" s="9">
+        <v>0</v>
+      </c>
+      <c r="X60" s="9">
+        <v>0.036363636363636362</v>
+      </c>
+      <c r="Y60" s="9">
+        <v>0.018181818181818181</v>
+      </c>
+      <c r="Z60" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="9">
+        <v>0.072727272727272724</v>
+      </c>
+      <c r="AB60" s="9">
+        <v>0.054545454545454543</v>
+      </c>
+      <c r="AC60" s="9">
+        <v>0.072727272727272724</v>
+      </c>
+      <c r="AD60" s="6">
+        <v>14</v>
+      </c>
+      <c r="AE60" s="6">
+        <v>12</v>
+      </c>
+      <c r="AF60" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG60" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH60" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI60" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ60" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK60" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL60" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM60" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN60" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO60" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP60" s="4">
         <v>58</v>
       </c>
@@ -9712,7 +10412,7 @@
         <v>19624</v>
       </c>
       <c r="B61" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C61" s="4">
         <v>51</v>
@@ -9740,35 +10440,93 @@
         <v>58</v>
       </c>
       <c r="L61" s="4"/>
-      <c r="M61" s="5"/>
-      <c r="N61" s="6"/>
-      <c r="O61" s="6"/>
-      <c r="P61" s="7"/>
-      <c r="Q61" s="8"/>
-      <c r="R61" s="8"/>
-      <c r="S61" s="8"/>
-      <c r="T61" s="9"/>
-      <c r="U61" s="9"/>
-      <c r="V61" s="9"/>
-      <c r="W61" s="9"/>
-      <c r="X61" s="9"/>
-      <c r="Y61" s="9"/>
-      <c r="Z61" s="9"/>
-      <c r="AA61" s="9"/>
-      <c r="AB61" s="9"/>
-      <c r="AC61" s="9"/>
-      <c r="AD61" s="6"/>
-      <c r="AE61" s="6"/>
-      <c r="AF61" s="6"/>
-      <c r="AG61" s="6"/>
-      <c r="AH61" s="6"/>
-      <c r="AI61" s="6"/>
-      <c r="AJ61" s="6"/>
-      <c r="AK61" s="6"/>
-      <c r="AL61" s="6"/>
-      <c r="AM61" s="6"/>
-      <c r="AN61" s="9"/>
-      <c r="AO61" s="6"/>
+      <c r="M61" s="5">
+        <v>9418.6399999999994</v>
+      </c>
+      <c r="N61" s="6">
+        <v>112</v>
+      </c>
+      <c r="O61" s="6">
+        <v>50</v>
+      </c>
+      <c r="P61" s="7">
+        <v>1.7236607142857143</v>
+      </c>
+      <c r="Q61" s="8">
+        <v>15.80578163265306</v>
+      </c>
+      <c r="R61" s="8">
+        <v>7.2055562499999999</v>
+      </c>
+      <c r="S61" s="8">
+        <v>7</v>
+      </c>
+      <c r="T61" s="9">
+        <v>0.59183673469387754</v>
+      </c>
+      <c r="U61" s="9">
+        <v>0.32000000000000001</v>
+      </c>
+      <c r="V61" s="9">
+        <v>0.059999999999999998</v>
+      </c>
+      <c r="W61" s="9">
+        <v>0</v>
+      </c>
+      <c r="X61" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="Y61" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="AB61" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="AC61" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="6">
+        <v>16</v>
+      </c>
+      <c r="AE61" s="6">
+        <v>16</v>
+      </c>
+      <c r="AF61" s="6">
+        <v>3</v>
+      </c>
+      <c r="AG61" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="6">
+        <v>10</v>
+      </c>
+      <c r="AI61" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ61" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK61" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL61" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM61" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN61" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO61" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP61" s="4">
         <v>58</v>
       </c>
@@ -9964,7 +10722,7 @@
         <v>19632</v>
       </c>
       <c r="B63" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C63" s="4">
         <v>51</v>
@@ -9994,8 +10752,12 @@
         <v>58</v>
       </c>
       <c r="L63" s="4"/>
-      <c r="M63" s="5"/>
-      <c r="N63" s="6"/>
+      <c r="M63" s="5">
+        <v>0</v>
+      </c>
+      <c r="N63" s="6">
+        <v>0</v>
+      </c>
       <c r="O63" s="6"/>
       <c r="P63" s="7"/>
       <c r="Q63" s="8"/>
@@ -11098,7 +11860,7 @@
         <v>19649</v>
       </c>
       <c r="B71" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C71" s="4">
         <v>51</v>
@@ -11126,35 +11888,93 @@
         <v>58</v>
       </c>
       <c r="L71" s="4"/>
-      <c r="M71" s="5"/>
-      <c r="N71" s="6"/>
-      <c r="O71" s="6"/>
-      <c r="P71" s="7"/>
-      <c r="Q71" s="8"/>
-      <c r="R71" s="8"/>
-      <c r="S71" s="8"/>
-      <c r="T71" s="9"/>
-      <c r="U71" s="9"/>
-      <c r="V71" s="9"/>
-      <c r="W71" s="9"/>
-      <c r="X71" s="9"/>
-      <c r="Y71" s="9"/>
-      <c r="Z71" s="9"/>
-      <c r="AA71" s="9"/>
-      <c r="AB71" s="9"/>
-      <c r="AC71" s="9"/>
-      <c r="AD71" s="6"/>
-      <c r="AE71" s="6"/>
-      <c r="AF71" s="6"/>
-      <c r="AG71" s="6"/>
-      <c r="AH71" s="6"/>
-      <c r="AI71" s="6"/>
-      <c r="AJ71" s="6"/>
-      <c r="AK71" s="6"/>
-      <c r="AL71" s="6"/>
-      <c r="AM71" s="6"/>
-      <c r="AN71" s="9"/>
-      <c r="AO71" s="6"/>
+      <c r="M71" s="5">
+        <v>12629.17</v>
+      </c>
+      <c r="N71" s="6">
+        <v>150</v>
+      </c>
+      <c r="O71" s="6">
+        <v>78</v>
+      </c>
+      <c r="P71" s="7">
+        <v>10.787126206896552</v>
+      </c>
+      <c r="Q71" s="8">
+        <v>34.100426923076917</v>
+      </c>
+      <c r="R71" s="8">
+        <v>15.203880821917808</v>
+      </c>
+      <c r="S71" s="8">
+        <v>8</v>
+      </c>
+      <c r="T71" s="9">
+        <v>0.17948717948717949</v>
+      </c>
+      <c r="U71" s="9">
+        <v>0.11538461538461539</v>
+      </c>
+      <c r="V71" s="9">
+        <v>0.01282051282051282</v>
+      </c>
+      <c r="W71" s="9">
+        <v>0</v>
+      </c>
+      <c r="X71" s="9">
+        <v>0.038461538461538464</v>
+      </c>
+      <c r="Y71" s="9">
+        <v>0.02564102564102564</v>
+      </c>
+      <c r="Z71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="9">
+        <v>0.089743589743589744</v>
+      </c>
+      <c r="AB71" s="9">
+        <v>0.01282051282051282</v>
+      </c>
+      <c r="AC71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD71" s="6">
+        <v>14</v>
+      </c>
+      <c r="AE71" s="6">
+        <v>9</v>
+      </c>
+      <c r="AF71" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI71" s="6">
+        <v>2</v>
+      </c>
+      <c r="AJ71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="6">
+        <v>7</v>
+      </c>
+      <c r="AL71" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO71" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP71" s="4">
         <v>58</v>
       </c>
@@ -11602,7 +12422,7 @@
         <v>19657</v>
       </c>
       <c r="B75" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C75" s="4">
         <v>51</v>
@@ -11632,35 +12452,93 @@
         <v>58</v>
       </c>
       <c r="L75" s="4"/>
-      <c r="M75" s="5"/>
-      <c r="N75" s="6"/>
-      <c r="O75" s="6"/>
-      <c r="P75" s="7"/>
-      <c r="Q75" s="8"/>
-      <c r="R75" s="8"/>
-      <c r="S75" s="8"/>
-      <c r="T75" s="9"/>
-      <c r="U75" s="9"/>
-      <c r="V75" s="9"/>
-      <c r="W75" s="9"/>
-      <c r="X75" s="9"/>
-      <c r="Y75" s="9"/>
-      <c r="Z75" s="9"/>
-      <c r="AA75" s="9"/>
-      <c r="AB75" s="9"/>
-      <c r="AC75" s="9"/>
-      <c r="AD75" s="6"/>
-      <c r="AE75" s="6"/>
-      <c r="AF75" s="6"/>
-      <c r="AG75" s="6"/>
-      <c r="AH75" s="6"/>
-      <c r="AI75" s="6"/>
-      <c r="AJ75" s="6"/>
-      <c r="AK75" s="6"/>
-      <c r="AL75" s="6"/>
-      <c r="AM75" s="6"/>
-      <c r="AN75" s="9"/>
-      <c r="AO75" s="6"/>
+      <c r="M75" s="5">
+        <v>7000.5900000000001</v>
+      </c>
+      <c r="N75" s="6">
+        <v>80</v>
+      </c>
+      <c r="O75" s="6">
+        <v>34</v>
+      </c>
+      <c r="P75" s="7">
+        <v>4.8222972972972977</v>
+      </c>
+      <c r="Q75" s="8">
+        <v>19.089214705882355</v>
+      </c>
+      <c r="R75" s="8">
+        <v>7.0024500000000005</v>
+      </c>
+      <c r="S75" s="8">
+        <v>7</v>
+      </c>
+      <c r="T75" s="9">
+        <v>0.35294117647058826</v>
+      </c>
+      <c r="U75" s="9">
+        <v>0.29411764705882354</v>
+      </c>
+      <c r="V75" s="9">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="W75" s="9">
+        <v>0</v>
+      </c>
+      <c r="X75" s="9">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="Y75" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="9">
+        <v>0.17647058823529413</v>
+      </c>
+      <c r="AC75" s="9">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="AD75" s="6">
+        <v>10</v>
+      </c>
+      <c r="AE75" s="6">
+        <v>10</v>
+      </c>
+      <c r="AF75" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL75" s="6">
+        <v>6</v>
+      </c>
+      <c r="AM75" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP75" s="4">
         <v>58</v>
       </c>
@@ -11701,7 +12579,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>51</v>
@@ -11729,35 +12607,93 @@
         <v>58</v>
       </c>
       <c r="L76" s="4"/>
-      <c r="M76" s="5"/>
-      <c r="N76" s="6"/>
-      <c r="O76" s="6"/>
-      <c r="P76" s="7"/>
-      <c r="Q76" s="8"/>
-      <c r="R76" s="8"/>
-      <c r="S76" s="8"/>
-      <c r="T76" s="9"/>
-      <c r="U76" s="9"/>
-      <c r="V76" s="9"/>
-      <c r="W76" s="9"/>
-      <c r="X76" s="9"/>
-      <c r="Y76" s="9"/>
-      <c r="Z76" s="9"/>
-      <c r="AA76" s="9"/>
-      <c r="AB76" s="9"/>
-      <c r="AC76" s="9"/>
-      <c r="AD76" s="6"/>
-      <c r="AE76" s="6"/>
-      <c r="AF76" s="6"/>
-      <c r="AG76" s="6"/>
-      <c r="AH76" s="6"/>
-      <c r="AI76" s="6"/>
-      <c r="AJ76" s="6"/>
-      <c r="AK76" s="6"/>
-      <c r="AL76" s="6"/>
-      <c r="AM76" s="6"/>
-      <c r="AN76" s="9"/>
-      <c r="AO76" s="6"/>
+      <c r="M76" s="5">
+        <v>9678.9500000000007</v>
+      </c>
+      <c r="N76" s="6">
+        <v>111</v>
+      </c>
+      <c r="O76" s="6">
+        <v>67</v>
+      </c>
+      <c r="P76" s="7">
+        <v>2.5999999999999996</v>
+      </c>
+      <c r="Q76" s="8">
+        <v>20.515422388059701</v>
+      </c>
+      <c r="R76" s="8">
+        <v>9.3955031746031743</v>
+      </c>
+      <c r="S76" s="8">
+        <v>9</v>
+      </c>
+      <c r="T76" s="9">
+        <v>0.26865671641791045</v>
+      </c>
+      <c r="U76" s="9">
+        <v>0.41791044776119401</v>
+      </c>
+      <c r="V76" s="9">
+        <v>0.014925373134328358</v>
+      </c>
+      <c r="W76" s="9">
+        <v>0</v>
+      </c>
+      <c r="X76" s="9">
+        <v>0.089552238805970144</v>
+      </c>
+      <c r="Y76" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="9">
+        <v>0.089552238805970144</v>
+      </c>
+      <c r="AB76" s="9">
+        <v>0.044776119402985072</v>
+      </c>
+      <c r="AC76" s="9">
+        <v>0.23880597014925373</v>
+      </c>
+      <c r="AD76" s="6">
+        <v>32</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>28</v>
+      </c>
+      <c r="AF76" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="6">
+        <v>6</v>
+      </c>
+      <c r="AI76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK76" s="6">
+        <v>6</v>
+      </c>
+      <c r="AL76" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM76" s="6">
+        <v>16</v>
+      </c>
+      <c r="AN76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO76" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP76" s="4">
         <v>58</v>
       </c>
@@ -12108,7 +13044,7 @@
         <v>19671</v>
       </c>
       <c r="B79" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C79" s="4">
         <v>51</v>
@@ -12138,35 +13074,93 @@
         <v>58</v>
       </c>
       <c r="L79" s="4"/>
-      <c r="M79" s="5"/>
-      <c r="N79" s="6"/>
-      <c r="O79" s="6"/>
-      <c r="P79" s="7"/>
-      <c r="Q79" s="8"/>
-      <c r="R79" s="8"/>
-      <c r="S79" s="8"/>
-      <c r="T79" s="9"/>
-      <c r="U79" s="9"/>
-      <c r="V79" s="9"/>
-      <c r="W79" s="9"/>
-      <c r="X79" s="9"/>
-      <c r="Y79" s="9"/>
-      <c r="Z79" s="9"/>
-      <c r="AA79" s="9"/>
-      <c r="AB79" s="9"/>
-      <c r="AC79" s="9"/>
-      <c r="AD79" s="6"/>
-      <c r="AE79" s="6"/>
-      <c r="AF79" s="6"/>
-      <c r="AG79" s="6"/>
-      <c r="AH79" s="6"/>
-      <c r="AI79" s="6"/>
-      <c r="AJ79" s="6"/>
-      <c r="AK79" s="6"/>
-      <c r="AL79" s="6"/>
-      <c r="AM79" s="6"/>
-      <c r="AN79" s="9"/>
-      <c r="AO79" s="6"/>
+      <c r="M79" s="5">
+        <v>9858.0300000000007</v>
+      </c>
+      <c r="N79" s="6">
+        <v>111</v>
+      </c>
+      <c r="O79" s="6">
+        <v>60</v>
+      </c>
+      <c r="P79" s="7">
+        <v>8.0938441441441444</v>
+      </c>
+      <c r="Q79" s="8">
+        <v>29.423333333333336</v>
+      </c>
+      <c r="R79" s="8">
+        <v>14.139655172413793</v>
+      </c>
+      <c r="S79" s="8">
+        <v>7</v>
+      </c>
+      <c r="T79" s="9">
+        <v>0.11666666666666667</v>
+      </c>
+      <c r="U79" s="9">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="V79" s="9">
+        <v>0</v>
+      </c>
+      <c r="W79" s="9">
+        <v>0</v>
+      </c>
+      <c r="X79" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y79" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z79" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA79" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="AB79" s="9">
+        <v>0.016666666666666666</v>
+      </c>
+      <c r="AC79" s="9">
+        <v>0.066666666666666666</v>
+      </c>
+      <c r="AD79" s="6">
+        <v>8</v>
+      </c>
+      <c r="AE79" s="6">
+        <v>8</v>
+      </c>
+      <c r="AF79" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG79" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH79" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI79" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ79" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK79" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL79" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM79" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN79" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO79" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP79" s="4">
         <v>58</v>
       </c>
@@ -12519,7 +13513,7 @@
         <v>19679</v>
       </c>
       <c r="B82" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C82" s="4">
         <v>51</v>
@@ -12549,8 +13543,12 @@
         <v>58</v>
       </c>
       <c r="L82" s="4"/>
-      <c r="M82" s="5"/>
-      <c r="N82" s="6"/>
+      <c r="M82" s="5">
+        <v>0</v>
+      </c>
+      <c r="N82" s="6">
+        <v>0</v>
+      </c>
       <c r="O82" s="6"/>
       <c r="P82" s="7"/>
       <c r="Q82" s="8"/>
@@ -16138,7 +17136,7 @@
         <v>19727</v>
       </c>
       <c r="B107" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C107" s="4">
         <v>51</v>
@@ -16168,35 +17166,93 @@
         <v>58</v>
       </c>
       <c r="L107" s="4"/>
-      <c r="M107" s="5"/>
-      <c r="N107" s="6"/>
-      <c r="O107" s="6"/>
-      <c r="P107" s="7"/>
-      <c r="Q107" s="8"/>
-      <c r="R107" s="8"/>
-      <c r="S107" s="8"/>
-      <c r="T107" s="9"/>
-      <c r="U107" s="9"/>
-      <c r="V107" s="9"/>
-      <c r="W107" s="9"/>
-      <c r="X107" s="9"/>
-      <c r="Y107" s="9"/>
-      <c r="Z107" s="9"/>
-      <c r="AA107" s="9"/>
-      <c r="AB107" s="9"/>
-      <c r="AC107" s="9"/>
-      <c r="AD107" s="6"/>
-      <c r="AE107" s="6"/>
-      <c r="AF107" s="6"/>
-      <c r="AG107" s="6"/>
-      <c r="AH107" s="6"/>
-      <c r="AI107" s="6"/>
-      <c r="AJ107" s="6"/>
-      <c r="AK107" s="6"/>
-      <c r="AL107" s="6"/>
-      <c r="AM107" s="6"/>
-      <c r="AN107" s="9"/>
-      <c r="AO107" s="6"/>
+      <c r="M107" s="5">
+        <v>5836.6499999999996</v>
+      </c>
+      <c r="N107" s="6">
+        <v>69</v>
+      </c>
+      <c r="O107" s="6">
+        <v>51</v>
+      </c>
+      <c r="P107" s="7">
+        <v>15.506102816901407</v>
+      </c>
+      <c r="Q107" s="8">
+        <v>39.25424901960784</v>
+      </c>
+      <c r="R107" s="8">
+        <v>16.575666000000002</v>
+      </c>
+      <c r="S107" s="8">
+        <v>7</v>
+      </c>
+      <c r="T107" s="9">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="U107" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="V107" s="9">
+        <v>0.078431372549019607</v>
+      </c>
+      <c r="W107" s="9">
+        <v>0</v>
+      </c>
+      <c r="X107" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y107" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z107" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA107" s="9">
+        <v>0.078431372549019607</v>
+      </c>
+      <c r="AB107" s="9">
+        <v>0.078431372549019607</v>
+      </c>
+      <c r="AC107" s="9">
+        <v>0.039215686274509803</v>
+      </c>
+      <c r="AD107" s="6">
+        <v>17</v>
+      </c>
+      <c r="AE107" s="6">
+        <v>17</v>
+      </c>
+      <c r="AF107" s="6">
+        <v>4</v>
+      </c>
+      <c r="AG107" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH107" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI107" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ107" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK107" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL107" s="6">
+        <v>4</v>
+      </c>
+      <c r="AM107" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN107" s="9">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="AO107" s="6">
+        <v>3</v>
+      </c>
       <c t="s" r="AP107" s="4">
         <v>58</v>
       </c>
@@ -16626,7 +17682,9 @@
       <c r="N111" s="6">
         <v>14</v>
       </c>
-      <c r="O111" s="6"/>
+      <c r="O111" s="6">
+        <v>13</v>
+      </c>
       <c r="P111" s="7">
         <v>6.8440500000000002</v>
       </c>
@@ -16636,31 +17694,75 @@
       <c r="R111" s="8">
         <v>1.3525615384615386</v>
       </c>
-      <c r="S111" s="8"/>
+      <c r="S111" s="8">
+        <v>7</v>
+      </c>
       <c r="T111" s="9">
         <v>0.53846153846153844</v>
       </c>
-      <c r="U111" s="9"/>
-      <c r="V111" s="9"/>
-      <c r="W111" s="9"/>
-      <c r="X111" s="9"/>
-      <c r="Y111" s="9"/>
-      <c r="Z111" s="9"/>
-      <c r="AA111" s="9"/>
-      <c r="AB111" s="9"/>
-      <c r="AC111" s="9"/>
-      <c r="AD111" s="6"/>
-      <c r="AE111" s="6"/>
-      <c r="AF111" s="6"/>
-      <c r="AG111" s="6"/>
-      <c r="AH111" s="6"/>
-      <c r="AI111" s="6"/>
-      <c r="AJ111" s="6"/>
-      <c r="AK111" s="6"/>
-      <c r="AL111" s="6"/>
-      <c r="AM111" s="6"/>
-      <c r="AN111" s="9"/>
-      <c r="AO111" s="6"/>
+      <c r="U111" s="9">
+        <v>0</v>
+      </c>
+      <c r="V111" s="9">
+        <v>0</v>
+      </c>
+      <c r="W111" s="9">
+        <v>0</v>
+      </c>
+      <c r="X111" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y111" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO111" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP111" s="4">
         <v>58</v>
       </c>
@@ -19870,7 +20972,7 @@
         <v>19775</v>
       </c>
       <c r="B133" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C133" s="4">
         <v>51</v>
@@ -19900,35 +21002,93 @@
         <v>58</v>
       </c>
       <c r="L133" s="4"/>
-      <c r="M133" s="5"/>
-      <c r="N133" s="6"/>
-      <c r="O133" s="6"/>
-      <c r="P133" s="7"/>
-      <c r="Q133" s="8"/>
-      <c r="R133" s="8"/>
-      <c r="S133" s="8"/>
-      <c r="T133" s="9"/>
-      <c r="U133" s="9"/>
-      <c r="V133" s="9"/>
-      <c r="W133" s="9"/>
-      <c r="X133" s="9"/>
-      <c r="Y133" s="9"/>
-      <c r="Z133" s="9"/>
-      <c r="AA133" s="9"/>
-      <c r="AB133" s="9"/>
-      <c r="AC133" s="9"/>
-      <c r="AD133" s="6"/>
-      <c r="AE133" s="6"/>
-      <c r="AF133" s="6"/>
-      <c r="AG133" s="6"/>
-      <c r="AH133" s="6"/>
-      <c r="AI133" s="6"/>
-      <c r="AJ133" s="6"/>
-      <c r="AK133" s="6"/>
-      <c r="AL133" s="6"/>
-      <c r="AM133" s="6"/>
-      <c r="AN133" s="9"/>
-      <c r="AO133" s="6"/>
+      <c r="M133" s="5">
+        <v>7065.0200000000004</v>
+      </c>
+      <c r="N133" s="6">
+        <v>74</v>
+      </c>
+      <c r="O133" s="6">
+        <v>40</v>
+      </c>
+      <c r="P133" s="7">
+        <v>13.40529411764706</v>
+      </c>
+      <c r="Q133" s="8">
+        <v>38.266667499999997</v>
+      </c>
+      <c r="R133" s="8">
+        <v>15.927027027027027</v>
+      </c>
+      <c r="S133" s="8">
+        <v>7</v>
+      </c>
+      <c r="T133" s="9">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="U133" s="9">
+        <v>0.14999999999999999</v>
+      </c>
+      <c r="V133" s="9">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="W133" s="9">
+        <v>0</v>
+      </c>
+      <c r="X133" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y133" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z133" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA133" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="AB133" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC133" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD133" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE133" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF133" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG133" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH133" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI133" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ133" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK133" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL133" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM133" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN133" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO133" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP133" s="4">
         <v>58</v>
       </c>
@@ -20283,7 +21443,7 @@
         <v>19785</v>
       </c>
       <c r="B136" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C136" s="4">
         <v>51</v>
@@ -20313,35 +21473,93 @@
         <v>58</v>
       </c>
       <c r="L136" s="4"/>
-      <c r="M136" s="5"/>
-      <c r="N136" s="6"/>
-      <c r="O136" s="6"/>
-      <c r="P136" s="7"/>
-      <c r="Q136" s="8"/>
-      <c r="R136" s="8"/>
-      <c r="S136" s="8"/>
-      <c r="T136" s="9"/>
-      <c r="U136" s="9"/>
-      <c r="V136" s="9"/>
-      <c r="W136" s="9"/>
-      <c r="X136" s="9"/>
-      <c r="Y136" s="9"/>
-      <c r="Z136" s="9"/>
-      <c r="AA136" s="9"/>
-      <c r="AB136" s="9"/>
-      <c r="AC136" s="9"/>
-      <c r="AD136" s="6"/>
-      <c r="AE136" s="6"/>
-      <c r="AF136" s="6"/>
-      <c r="AG136" s="6"/>
-      <c r="AH136" s="6"/>
-      <c r="AI136" s="6"/>
-      <c r="AJ136" s="6"/>
-      <c r="AK136" s="6"/>
-      <c r="AL136" s="6"/>
-      <c r="AM136" s="6"/>
-      <c r="AN136" s="9"/>
-      <c r="AO136" s="6"/>
+      <c r="M136" s="5">
+        <v>10018.73</v>
+      </c>
+      <c r="N136" s="6">
+        <v>90</v>
+      </c>
+      <c r="O136" s="6">
+        <v>36</v>
+      </c>
+      <c r="P136" s="7">
+        <v>4.4970366666666663</v>
+      </c>
+      <c r="Q136" s="8">
+        <v>16.395369444444444</v>
+      </c>
+      <c r="R136" s="8">
+        <v>5.130477142857143</v>
+      </c>
+      <c r="S136" s="8">
+        <v>7</v>
+      </c>
+      <c r="T136" s="9">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="U136" s="9">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="V136" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="W136" s="9">
+        <v>0</v>
+      </c>
+      <c r="X136" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y136" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z136" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA136" s="9">
+        <v>0.027777777777777776</v>
+      </c>
+      <c r="AB136" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC136" s="9">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AD136" s="6">
+        <v>8</v>
+      </c>
+      <c r="AE136" s="6">
+        <v>8</v>
+      </c>
+      <c r="AF136" s="6">
+        <v>3</v>
+      </c>
+      <c r="AG136" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH136" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI136" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ136" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK136" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL136" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM136" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN136" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO136" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP136" s="4">
         <v>58</v>
       </c>
@@ -20382,7 +21600,7 @@
         <v>19787</v>
       </c>
       <c r="B137" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C137" s="4">
         <v>51</v>
@@ -20410,35 +21628,93 @@
         <v>58</v>
       </c>
       <c r="L137" s="4"/>
-      <c r="M137" s="5"/>
-      <c r="N137" s="6"/>
-      <c r="O137" s="6"/>
-      <c r="P137" s="7"/>
-      <c r="Q137" s="8"/>
-      <c r="R137" s="8"/>
-      <c r="S137" s="8"/>
-      <c r="T137" s="9"/>
-      <c r="U137" s="9"/>
-      <c r="V137" s="9"/>
-      <c r="W137" s="9"/>
-      <c r="X137" s="9"/>
-      <c r="Y137" s="9"/>
-      <c r="Z137" s="9"/>
-      <c r="AA137" s="9"/>
-      <c r="AB137" s="9"/>
-      <c r="AC137" s="9"/>
-      <c r="AD137" s="6"/>
-      <c r="AE137" s="6"/>
-      <c r="AF137" s="6"/>
-      <c r="AG137" s="6"/>
-      <c r="AH137" s="6"/>
-      <c r="AI137" s="6"/>
-      <c r="AJ137" s="6"/>
-      <c r="AK137" s="6"/>
-      <c r="AL137" s="6"/>
-      <c r="AM137" s="6"/>
-      <c r="AN137" s="9"/>
-      <c r="AO137" s="6"/>
+      <c r="M137" s="5">
+        <v>6397.0200000000004</v>
+      </c>
+      <c r="N137" s="6">
+        <v>71</v>
+      </c>
+      <c r="O137" s="6">
+        <v>23</v>
+      </c>
+      <c r="P137" s="7">
+        <v>5.7734229729729725</v>
+      </c>
+      <c r="Q137" s="8">
+        <v>16.622465217391305</v>
+      </c>
+      <c r="R137" s="8">
+        <v>4.0608695652173914</v>
+      </c>
+      <c r="S137" s="8">
+        <v>7</v>
+      </c>
+      <c r="T137" s="9">
+        <v>0.30434782608695654</v>
+      </c>
+      <c r="U137" s="9">
+        <v>0</v>
+      </c>
+      <c r="V137" s="9">
+        <v>0</v>
+      </c>
+      <c r="W137" s="9">
+        <v>0</v>
+      </c>
+      <c r="X137" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y137" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z137" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA137" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB137" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC137" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD137" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE137" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF137" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG137" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH137" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI137" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ137" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK137" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL137" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM137" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN137" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO137" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP137" s="4">
         <v>58</v>
       </c>
@@ -21927,7 +23203,7 @@
         <v>19809</v>
       </c>
       <c r="B148" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C148" s="4">
         <v>51</v>
@@ -21957,35 +23233,93 @@
         <v>58</v>
       </c>
       <c r="L148" s="4"/>
-      <c r="M148" s="5"/>
-      <c r="N148" s="6"/>
-      <c r="O148" s="6"/>
-      <c r="P148" s="7"/>
-      <c r="Q148" s="8"/>
-      <c r="R148" s="8"/>
-      <c r="S148" s="8"/>
-      <c r="T148" s="9"/>
-      <c r="U148" s="9"/>
-      <c r="V148" s="9"/>
-      <c r="W148" s="9"/>
-      <c r="X148" s="9"/>
-      <c r="Y148" s="9"/>
-      <c r="Z148" s="9"/>
-      <c r="AA148" s="9"/>
-      <c r="AB148" s="9"/>
-      <c r="AC148" s="9"/>
-      <c r="AD148" s="6"/>
-      <c r="AE148" s="6"/>
-      <c r="AF148" s="6"/>
-      <c r="AG148" s="6"/>
-      <c r="AH148" s="6"/>
-      <c r="AI148" s="6"/>
-      <c r="AJ148" s="6"/>
-      <c r="AK148" s="6"/>
-      <c r="AL148" s="6"/>
-      <c r="AM148" s="6"/>
-      <c r="AN148" s="9"/>
-      <c r="AO148" s="6"/>
+      <c r="M148" s="5">
+        <v>8590.9400000000005</v>
+      </c>
+      <c r="N148" s="6">
+        <v>91</v>
+      </c>
+      <c r="O148" s="6">
+        <v>71</v>
+      </c>
+      <c r="P148" s="7">
+        <v>10.023147777777778</v>
+      </c>
+      <c r="Q148" s="8">
+        <v>37.878404225352114</v>
+      </c>
+      <c r="R148" s="8">
+        <v>20.575245588235294</v>
+      </c>
+      <c r="S148" s="8">
+        <v>8</v>
+      </c>
+      <c r="T148" s="9">
+        <v>0.070422535211267609</v>
+      </c>
+      <c r="U148" s="9">
+        <v>0.43661971830985913</v>
+      </c>
+      <c r="V148" s="9">
+        <v>0</v>
+      </c>
+      <c r="W148" s="9">
+        <v>0</v>
+      </c>
+      <c r="X148" s="9">
+        <v>0.014084507042253521</v>
+      </c>
+      <c r="Y148" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z148" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA148" s="9">
+        <v>0.056338028169014086</v>
+      </c>
+      <c r="AB148" s="9">
+        <v>0.12676056338028169</v>
+      </c>
+      <c r="AC148" s="9">
+        <v>0.26760563380281688</v>
+      </c>
+      <c r="AD148" s="6">
+        <v>33</v>
+      </c>
+      <c r="AE148" s="6">
+        <v>31</v>
+      </c>
+      <c r="AF148" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG148" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH148" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI148" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ148" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK148" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL148" s="6">
+        <v>9</v>
+      </c>
+      <c r="AM148" s="6">
+        <v>19</v>
+      </c>
+      <c r="AN148" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO148" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP148" s="4">
         <v>58</v>
       </c>
@@ -23454,7 +24788,9 @@
       <c r="N159" s="6">
         <v>85</v>
       </c>
-      <c r="O159" s="6"/>
+      <c r="O159" s="6">
+        <v>70</v>
+      </c>
       <c r="P159" s="7">
         <v>5.3440476190476192</v>
       </c>
@@ -23464,31 +24800,75 @@
       <c r="R159" s="8">
         <v>6.1600000000000001</v>
       </c>
-      <c r="S159" s="8"/>
+      <c r="S159" s="8">
+        <v>7</v>
+      </c>
       <c r="T159" s="9">
         <v>0.37142857142857144</v>
       </c>
-      <c r="U159" s="9"/>
-      <c r="V159" s="9"/>
-      <c r="W159" s="9"/>
-      <c r="X159" s="9"/>
-      <c r="Y159" s="9"/>
-      <c r="Z159" s="9"/>
-      <c r="AA159" s="9"/>
-      <c r="AB159" s="9"/>
-      <c r="AC159" s="9"/>
-      <c r="AD159" s="6"/>
-      <c r="AE159" s="6"/>
-      <c r="AF159" s="6"/>
-      <c r="AG159" s="6"/>
-      <c r="AH159" s="6"/>
-      <c r="AI159" s="6"/>
-      <c r="AJ159" s="6"/>
-      <c r="AK159" s="6"/>
-      <c r="AL159" s="6"/>
-      <c r="AM159" s="6"/>
-      <c r="AN159" s="9"/>
-      <c r="AO159" s="6"/>
+      <c r="U159" s="9">
+        <v>0.085714285714285715</v>
+      </c>
+      <c r="V159" s="9">
+        <v>0</v>
+      </c>
+      <c r="W159" s="9">
+        <v>0</v>
+      </c>
+      <c r="X159" s="9">
+        <v>0.057142857142857141</v>
+      </c>
+      <c r="Y159" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z159" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA159" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB159" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC159" s="9">
+        <v>0.028571428571428571</v>
+      </c>
+      <c r="AD159" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE159" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF159" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG159" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH159" s="6">
+        <v>4</v>
+      </c>
+      <c r="AI159" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ159" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK159" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL159" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM159" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN159" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO159" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP159" s="4">
         <v>58</v>
       </c>
@@ -23785,7 +25165,7 @@
         <v>19872</v>
       </c>
       <c r="B162" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C162" s="4">
         <v>51</v>
@@ -23815,35 +25195,93 @@
         <v>58</v>
       </c>
       <c r="L162" s="4"/>
-      <c r="M162" s="5"/>
-      <c r="N162" s="6"/>
-      <c r="O162" s="6"/>
-      <c r="P162" s="7"/>
-      <c r="Q162" s="8"/>
-      <c r="R162" s="8"/>
-      <c r="S162" s="8"/>
-      <c r="T162" s="9"/>
-      <c r="U162" s="9"/>
-      <c r="V162" s="9"/>
-      <c r="W162" s="9"/>
-      <c r="X162" s="9"/>
-      <c r="Y162" s="9"/>
-      <c r="Z162" s="9"/>
-      <c r="AA162" s="9"/>
-      <c r="AB162" s="9"/>
-      <c r="AC162" s="9"/>
-      <c r="AD162" s="6"/>
-      <c r="AE162" s="6"/>
-      <c r="AF162" s="6"/>
-      <c r="AG162" s="6"/>
-      <c r="AH162" s="6"/>
-      <c r="AI162" s="6"/>
-      <c r="AJ162" s="6"/>
-      <c r="AK162" s="6"/>
-      <c r="AL162" s="6"/>
-      <c r="AM162" s="6"/>
-      <c r="AN162" s="9"/>
-      <c r="AO162" s="6"/>
+      <c r="M162" s="5">
+        <v>7585.5799999999999</v>
+      </c>
+      <c r="N162" s="6">
+        <v>86</v>
+      </c>
+      <c r="O162" s="6">
+        <v>40</v>
+      </c>
+      <c r="P162" s="7">
+        <v>12.59083375</v>
+      </c>
+      <c r="Q162" s="8">
+        <v>26.890417500000002</v>
+      </c>
+      <c r="R162" s="8">
+        <v>7.3198189189189193</v>
+      </c>
+      <c r="S162" s="8">
+        <v>8</v>
+      </c>
+      <c r="T162" s="9">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="U162" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="V162" s="9">
+        <v>0</v>
+      </c>
+      <c r="W162" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="X162" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y162" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z162" s="9">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="AA162" s="9">
+        <v>0.074999999999999997</v>
+      </c>
+      <c r="AB162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC162" s="9">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="AD162" s="6">
+        <v>20</v>
+      </c>
+      <c r="AE162" s="6">
+        <v>20</v>
+      </c>
+      <c r="AF162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG162" s="6">
+        <v>2</v>
+      </c>
+      <c r="AH162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ162" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK162" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM162" s="6">
+        <v>16</v>
+      </c>
+      <c r="AN162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO162" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP162" s="4">
         <v>58</v>
       </c>
@@ -25708,7 +27146,7 @@
         <v>19897</v>
       </c>
       <c r="B175" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C175" s="4">
         <v>51</v>
@@ -25738,35 +27176,93 @@
         <v>58</v>
       </c>
       <c r="L175" s="4"/>
-      <c r="M175" s="5"/>
-      <c r="N175" s="6"/>
-      <c r="O175" s="6"/>
-      <c r="P175" s="7"/>
-      <c r="Q175" s="8"/>
-      <c r="R175" s="8"/>
-      <c r="S175" s="8"/>
-      <c r="T175" s="9"/>
-      <c r="U175" s="9"/>
-      <c r="V175" s="9"/>
-      <c r="W175" s="9"/>
-      <c r="X175" s="9"/>
-      <c r="Y175" s="9"/>
-      <c r="Z175" s="9"/>
-      <c r="AA175" s="9"/>
-      <c r="AB175" s="9"/>
-      <c r="AC175" s="9"/>
-      <c r="AD175" s="6"/>
-      <c r="AE175" s="6"/>
-      <c r="AF175" s="6"/>
-      <c r="AG175" s="6"/>
-      <c r="AH175" s="6"/>
-      <c r="AI175" s="6"/>
-      <c r="AJ175" s="6"/>
-      <c r="AK175" s="6"/>
-      <c r="AL175" s="6"/>
-      <c r="AM175" s="6"/>
-      <c r="AN175" s="9"/>
-      <c r="AO175" s="6"/>
+      <c r="M175" s="5">
+        <v>7953.5299999999997</v>
+      </c>
+      <c r="N175" s="6">
+        <v>96</v>
+      </c>
+      <c r="O175" s="6">
+        <v>51</v>
+      </c>
+      <c r="P175" s="7">
+        <v>14.066111111111111</v>
+      </c>
+      <c r="Q175" s="8">
+        <v>26.107843137254903</v>
+      </c>
+      <c r="R175" s="8">
+        <v>5.9520408163265301</v>
+      </c>
+      <c r="S175" s="8">
+        <v>7</v>
+      </c>
+      <c r="T175" s="9">
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="U175" s="9">
+        <v>0.098039215686274508</v>
+      </c>
+      <c r="V175" s="9">
+        <v>0.019607843137254902</v>
+      </c>
+      <c r="W175" s="9">
+        <v>0.019607843137000001</v>
+      </c>
+      <c r="X175" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y175" s="9">
+        <v>0.019607843137254902</v>
+      </c>
+      <c r="Z175" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA175" s="9">
+        <v>0.078431372549019607</v>
+      </c>
+      <c r="AB175" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC175" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD175" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE175" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF175" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG175" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI175" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK175" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN175" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO175" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP175" s="4">
         <v>58</v>
       </c>
@@ -26900,7 +28396,7 @@
         <v>19912</v>
       </c>
       <c r="B183" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C183" s="4">
         <v>51</v>
@@ -26930,35 +28426,93 @@
         <v>58</v>
       </c>
       <c r="L183" s="4"/>
-      <c r="M183" s="5"/>
-      <c r="N183" s="6"/>
-      <c r="O183" s="6"/>
-      <c r="P183" s="7"/>
-      <c r="Q183" s="8"/>
-      <c r="R183" s="8"/>
-      <c r="S183" s="8"/>
-      <c r="T183" s="9"/>
-      <c r="U183" s="9"/>
-      <c r="V183" s="9"/>
-      <c r="W183" s="9"/>
-      <c r="X183" s="9"/>
-      <c r="Y183" s="9"/>
-      <c r="Z183" s="9"/>
-      <c r="AA183" s="9"/>
-      <c r="AB183" s="9"/>
-      <c r="AC183" s="9"/>
-      <c r="AD183" s="6"/>
-      <c r="AE183" s="6"/>
-      <c r="AF183" s="6"/>
-      <c r="AG183" s="6"/>
-      <c r="AH183" s="6"/>
-      <c r="AI183" s="6"/>
-      <c r="AJ183" s="6"/>
-      <c r="AK183" s="6"/>
-      <c r="AL183" s="6"/>
-      <c r="AM183" s="6"/>
-      <c r="AN183" s="9"/>
-      <c r="AO183" s="6"/>
+      <c r="M183" s="5">
+        <v>7506.04</v>
+      </c>
+      <c r="N183" s="6">
+        <v>87</v>
+      </c>
+      <c r="O183" s="6">
+        <v>56</v>
+      </c>
+      <c r="P183" s="7">
+        <v>7.8571709302325576</v>
+      </c>
+      <c r="Q183" s="8">
+        <v>19.29791607142857</v>
+      </c>
+      <c r="R183" s="8">
+        <v>5.4692307692307685</v>
+      </c>
+      <c r="S183" s="8">
+        <v>8</v>
+      </c>
+      <c r="T183" s="9">
+        <v>0.26785714285714285</v>
+      </c>
+      <c r="U183" s="9">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="V183" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="W183" s="9">
+        <v>0.017857142857000002</v>
+      </c>
+      <c r="X183" s="9">
+        <v>0.017857142857142856</v>
+      </c>
+      <c r="Y183" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z183" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA183" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="AB183" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC183" s="9">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="AD183" s="6">
+        <v>17</v>
+      </c>
+      <c r="AE183" s="6">
+        <v>16</v>
+      </c>
+      <c r="AF183" s="6">
+        <v>4</v>
+      </c>
+      <c r="AG183" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH183" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI183" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ183" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK183" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL183" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM183" s="6">
+        <v>8</v>
+      </c>
+      <c r="AN183" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO183" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP183" s="4">
         <v>58</v>
       </c>
@@ -27255,7 +28809,7 @@
         <v>19926</v>
       </c>
       <c r="B186" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C186" s="4">
         <v>51</v>
@@ -27285,35 +28839,93 @@
         <v>58</v>
       </c>
       <c r="L186" s="4"/>
-      <c r="M186" s="5"/>
-      <c r="N186" s="6"/>
-      <c r="O186" s="6"/>
-      <c r="P186" s="7"/>
-      <c r="Q186" s="8"/>
-      <c r="R186" s="8"/>
-      <c r="S186" s="8"/>
-      <c r="T186" s="9"/>
-      <c r="U186" s="9"/>
-      <c r="V186" s="9"/>
-      <c r="W186" s="9"/>
-      <c r="X186" s="9"/>
-      <c r="Y186" s="9"/>
-      <c r="Z186" s="9"/>
-      <c r="AA186" s="9"/>
-      <c r="AB186" s="9"/>
-      <c r="AC186" s="9"/>
-      <c r="AD186" s="6"/>
-      <c r="AE186" s="6"/>
-      <c r="AF186" s="6"/>
-      <c r="AG186" s="6"/>
-      <c r="AH186" s="6"/>
-      <c r="AI186" s="6"/>
-      <c r="AJ186" s="6"/>
-      <c r="AK186" s="6"/>
-      <c r="AL186" s="6"/>
-      <c r="AM186" s="6"/>
-      <c r="AN186" s="9"/>
-      <c r="AO186" s="6"/>
+      <c r="M186" s="5">
+        <v>2790.9000000000001</v>
+      </c>
+      <c r="N186" s="6">
+        <v>30</v>
+      </c>
+      <c r="O186" s="6">
+        <v>17</v>
+      </c>
+      <c r="P186" s="7">
+        <v>15.814584375000001</v>
+      </c>
+      <c r="Q186" s="8">
+        <v>32.026470588235298</v>
+      </c>
+      <c r="R186" s="8">
+        <v>9.2480411764705881</v>
+      </c>
+      <c r="S186" s="8">
+        <v>7</v>
+      </c>
+      <c r="T186" s="9">
+        <v>0</v>
+      </c>
+      <c r="U186" s="9">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="V186" s="9">
+        <v>0</v>
+      </c>
+      <c r="W186" s="9">
+        <v>0</v>
+      </c>
+      <c r="X186" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y186" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z186" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA186" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB186" s="9">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="AC186" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD186" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE186" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF186" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG186" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH186" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI186" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ186" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK186" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL186" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM186" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN186" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO186" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP186" s="4">
         <v>58</v>
       </c>
@@ -27354,7 +28966,7 @@
         <v>19927</v>
       </c>
       <c r="B187" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C187" s="4">
         <v>51</v>
@@ -27384,35 +28996,93 @@
         <v>58</v>
       </c>
       <c r="L187" s="4"/>
-      <c r="M187" s="5"/>
-      <c r="N187" s="6"/>
-      <c r="O187" s="6"/>
-      <c r="P187" s="7"/>
-      <c r="Q187" s="8"/>
-      <c r="R187" s="8"/>
-      <c r="S187" s="8"/>
-      <c r="T187" s="9"/>
-      <c r="U187" s="9"/>
-      <c r="V187" s="9"/>
-      <c r="W187" s="9"/>
-      <c r="X187" s="9"/>
-      <c r="Y187" s="9"/>
-      <c r="Z187" s="9"/>
-      <c r="AA187" s="9"/>
-      <c r="AB187" s="9"/>
-      <c r="AC187" s="9"/>
-      <c r="AD187" s="6"/>
-      <c r="AE187" s="6"/>
-      <c r="AF187" s="6"/>
-      <c r="AG187" s="6"/>
-      <c r="AH187" s="6"/>
-      <c r="AI187" s="6"/>
-      <c r="AJ187" s="6"/>
-      <c r="AK187" s="6"/>
-      <c r="AL187" s="6"/>
-      <c r="AM187" s="6"/>
-      <c r="AN187" s="9"/>
-      <c r="AO187" s="6"/>
+      <c r="M187" s="5">
+        <v>2316.8000000000002</v>
+      </c>
+      <c r="N187" s="6">
+        <v>33</v>
+      </c>
+      <c r="O187" s="6">
+        <v>26</v>
+      </c>
+      <c r="P187" s="7">
+        <v>10.768094285714286</v>
+      </c>
+      <c r="Q187" s="8">
+        <v>25.25</v>
+      </c>
+      <c r="R187" s="8">
+        <v>8.8019230769230763</v>
+      </c>
+      <c r="S187" s="8">
+        <v>7</v>
+      </c>
+      <c r="T187" s="9">
+        <v>0.19230769230769232</v>
+      </c>
+      <c r="U187" s="9">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="V187" s="9">
+        <v>0</v>
+      </c>
+      <c r="W187" s="9">
+        <v>0</v>
+      </c>
+      <c r="X187" s="9">
+        <v>0.038461538461538464</v>
+      </c>
+      <c r="Y187" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB187" s="9">
+        <v>0.038461538461538464</v>
+      </c>
+      <c r="AC187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD187" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE187" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH187" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL187" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO187" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP187" s="4">
         <v>58</v>
       </c>
@@ -27610,7 +29280,7 @@
         <v>19930</v>
       </c>
       <c r="B189" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C189" s="4">
         <v>51</v>
@@ -27640,35 +29310,93 @@
         <v>58</v>
       </c>
       <c r="L189" s="4"/>
-      <c r="M189" s="5"/>
-      <c r="N189" s="6"/>
-      <c r="O189" s="6"/>
-      <c r="P189" s="7"/>
-      <c r="Q189" s="8"/>
-      <c r="R189" s="8"/>
-      <c r="S189" s="8"/>
-      <c r="T189" s="9"/>
-      <c r="U189" s="9"/>
-      <c r="V189" s="9"/>
-      <c r="W189" s="9"/>
-      <c r="X189" s="9"/>
-      <c r="Y189" s="9"/>
-      <c r="Z189" s="9"/>
-      <c r="AA189" s="9"/>
-      <c r="AB189" s="9"/>
-      <c r="AC189" s="9"/>
-      <c r="AD189" s="6"/>
-      <c r="AE189" s="6"/>
-      <c r="AF189" s="6"/>
-      <c r="AG189" s="6"/>
-      <c r="AH189" s="6"/>
-      <c r="AI189" s="6"/>
-      <c r="AJ189" s="6"/>
-      <c r="AK189" s="6"/>
-      <c r="AL189" s="6"/>
-      <c r="AM189" s="6"/>
-      <c r="AN189" s="9"/>
-      <c r="AO189" s="6"/>
+      <c r="M189" s="5">
+        <v>8238.4099999999999</v>
+      </c>
+      <c r="N189" s="6">
+        <v>113</v>
+      </c>
+      <c r="O189" s="6">
+        <v>102</v>
+      </c>
+      <c r="P189" s="7">
+        <v>7.7990110169491533</v>
+      </c>
+      <c r="Q189" s="8">
+        <v>24.784640196078431</v>
+      </c>
+      <c r="R189" s="8">
+        <v>10.568229166666667</v>
+      </c>
+      <c r="S189" s="8">
+        <v>7</v>
+      </c>
+      <c r="T189" s="9">
+        <v>0.15686274509803921</v>
+      </c>
+      <c r="U189" s="9">
+        <v>0.55882352941176472</v>
+      </c>
+      <c r="V189" s="9">
+        <v>0</v>
+      </c>
+      <c r="W189" s="9">
+        <v>0</v>
+      </c>
+      <c r="X189" s="9">
+        <v>0.0098039215686274508</v>
+      </c>
+      <c r="Y189" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA189" s="9">
+        <v>0.078431372549019607</v>
+      </c>
+      <c r="AB189" s="9">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="AC189" s="9">
+        <v>0.50980392156862742</v>
+      </c>
+      <c r="AD189" s="6">
+        <v>64</v>
+      </c>
+      <c r="AE189" s="6">
+        <v>57</v>
+      </c>
+      <c r="AF189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH189" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK189" s="6">
+        <v>8</v>
+      </c>
+      <c r="AL189" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM189" s="6">
+        <v>52</v>
+      </c>
+      <c r="AN189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO189" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP189" s="4">
         <v>58</v>
       </c>
@@ -27709,7 +29437,7 @@
         <v>19931</v>
       </c>
       <c r="B190" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C190" s="4">
         <v>51</v>
@@ -27739,35 +29467,93 @@
         <v>58</v>
       </c>
       <c r="L190" s="4"/>
-      <c r="M190" s="5"/>
-      <c r="N190" s="6"/>
-      <c r="O190" s="6"/>
-      <c r="P190" s="7"/>
-      <c r="Q190" s="8"/>
-      <c r="R190" s="8"/>
-      <c r="S190" s="8"/>
-      <c r="T190" s="9"/>
-      <c r="U190" s="9"/>
-      <c r="V190" s="9"/>
-      <c r="W190" s="9"/>
-      <c r="X190" s="9"/>
-      <c r="Y190" s="9"/>
-      <c r="Z190" s="9"/>
-      <c r="AA190" s="9"/>
-      <c r="AB190" s="9"/>
-      <c r="AC190" s="9"/>
-      <c r="AD190" s="6"/>
-      <c r="AE190" s="6"/>
-      <c r="AF190" s="6"/>
-      <c r="AG190" s="6"/>
-      <c r="AH190" s="6"/>
-      <c r="AI190" s="6"/>
-      <c r="AJ190" s="6"/>
-      <c r="AK190" s="6"/>
-      <c r="AL190" s="6"/>
-      <c r="AM190" s="6"/>
-      <c r="AN190" s="9"/>
-      <c r="AO190" s="6"/>
+      <c r="M190" s="5">
+        <v>9142.7399999999998</v>
+      </c>
+      <c r="N190" s="6">
+        <v>102</v>
+      </c>
+      <c r="O190" s="6">
+        <v>42</v>
+      </c>
+      <c r="P190" s="7">
+        <v>6.79309797979798</v>
+      </c>
+      <c r="Q190" s="8">
+        <v>21.701190476190476</v>
+      </c>
+      <c r="R190" s="8">
+        <v>8.305128205128204</v>
+      </c>
+      <c r="S190" s="8">
+        <v>7</v>
+      </c>
+      <c r="T190" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="U190" s="9">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="V190" s="9">
+        <v>0</v>
+      </c>
+      <c r="W190" s="9">
+        <v>0</v>
+      </c>
+      <c r="X190" s="9">
+        <v>0.023809523809523808</v>
+      </c>
+      <c r="Y190" s="9">
+        <v>0.023809523809523808</v>
+      </c>
+      <c r="Z190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA190" s="9">
+        <v>0.11904761904761904</v>
+      </c>
+      <c r="AB190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC190" s="9">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="AD190" s="6">
+        <v>13</v>
+      </c>
+      <c r="AE190" s="6">
+        <v>12</v>
+      </c>
+      <c r="AF190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH190" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI190" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK190" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM190" s="6">
+        <v>6</v>
+      </c>
+      <c r="AN190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO190" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP190" s="4">
         <v>58</v>
       </c>
@@ -27965,7 +29751,7 @@
         <v>19936</v>
       </c>
       <c r="B192" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C192" s="4">
         <v>51</v>
@@ -27995,35 +29781,93 @@
         <v>58</v>
       </c>
       <c r="L192" s="4"/>
-      <c r="M192" s="5"/>
-      <c r="N192" s="6"/>
-      <c r="O192" s="6"/>
-      <c r="P192" s="7"/>
-      <c r="Q192" s="8"/>
-      <c r="R192" s="8"/>
-      <c r="S192" s="8"/>
-      <c r="T192" s="9"/>
-      <c r="U192" s="9"/>
-      <c r="V192" s="9"/>
-      <c r="W192" s="9"/>
-      <c r="X192" s="9"/>
-      <c r="Y192" s="9"/>
-      <c r="Z192" s="9"/>
-      <c r="AA192" s="9"/>
-      <c r="AB192" s="9"/>
-      <c r="AC192" s="9"/>
-      <c r="AD192" s="6"/>
-      <c r="AE192" s="6"/>
-      <c r="AF192" s="6"/>
-      <c r="AG192" s="6"/>
-      <c r="AH192" s="6"/>
-      <c r="AI192" s="6"/>
-      <c r="AJ192" s="6"/>
-      <c r="AK192" s="6"/>
-      <c r="AL192" s="6"/>
-      <c r="AM192" s="6"/>
-      <c r="AN192" s="9"/>
-      <c r="AO192" s="6"/>
+      <c r="M192" s="5">
+        <v>3889.4499999999998</v>
+      </c>
+      <c r="N192" s="6">
+        <v>41</v>
+      </c>
+      <c r="O192" s="6">
+        <v>25</v>
+      </c>
+      <c r="P192" s="7">
+        <v>4.4930902439024392</v>
+      </c>
+      <c r="Q192" s="8">
+        <v>34.464668000000003</v>
+      </c>
+      <c r="R192" s="8">
+        <v>23.026</v>
+      </c>
+      <c r="S192" s="8">
+        <v>7</v>
+      </c>
+      <c r="T192" s="9">
+        <v>0.080000000000000002</v>
+      </c>
+      <c r="U192" s="9">
+        <v>0.44</v>
+      </c>
+      <c r="V192" s="9">
+        <v>0</v>
+      </c>
+      <c r="W192" s="9">
+        <v>0</v>
+      </c>
+      <c r="X192" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="Y192" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z192" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA192" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB192" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="AC192" s="9">
+        <v>0.23999999999999999</v>
+      </c>
+      <c r="AD192" s="6">
+        <v>12</v>
+      </c>
+      <c r="AE192" s="6">
+        <v>11</v>
+      </c>
+      <c r="AF192" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG192" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH192" s="6">
+        <v>5</v>
+      </c>
+      <c r="AI192" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ192" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK192" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL192" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM192" s="6">
+        <v>6</v>
+      </c>
+      <c r="AN192" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO192" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP192" s="4">
         <v>58</v>
       </c>
@@ -28219,7 +30063,7 @@
         <v>19943</v>
       </c>
       <c r="B194" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C194" s="4">
         <v>51</v>
@@ -28249,35 +30093,93 @@
         <v>58</v>
       </c>
       <c r="L194" s="4"/>
-      <c r="M194" s="5"/>
-      <c r="N194" s="6"/>
-      <c r="O194" s="6"/>
-      <c r="P194" s="7"/>
-      <c r="Q194" s="8"/>
-      <c r="R194" s="8"/>
-      <c r="S194" s="8"/>
-      <c r="T194" s="9"/>
-      <c r="U194" s="9"/>
-      <c r="V194" s="9"/>
-      <c r="W194" s="9"/>
-      <c r="X194" s="9"/>
-      <c r="Y194" s="9"/>
-      <c r="Z194" s="9"/>
-      <c r="AA194" s="9"/>
-      <c r="AB194" s="9"/>
-      <c r="AC194" s="9"/>
-      <c r="AD194" s="6"/>
-      <c r="AE194" s="6"/>
-      <c r="AF194" s="6"/>
-      <c r="AG194" s="6"/>
-      <c r="AH194" s="6"/>
-      <c r="AI194" s="6"/>
-      <c r="AJ194" s="6"/>
-      <c r="AK194" s="6"/>
-      <c r="AL194" s="6"/>
-      <c r="AM194" s="6"/>
-      <c r="AN194" s="9"/>
-      <c r="AO194" s="6"/>
+      <c r="M194" s="5">
+        <v>3645</v>
+      </c>
+      <c r="N194" s="6">
+        <v>45</v>
+      </c>
+      <c r="O194" s="6">
+        <v>22</v>
+      </c>
+      <c r="P194" s="7">
+        <v>11.052897826086957</v>
+      </c>
+      <c r="Q194" s="8">
+        <v>28.507142857142856</v>
+      </c>
+      <c r="R194" s="8">
+        <v>11.055557142857143</v>
+      </c>
+      <c r="S194" s="8">
+        <v>7</v>
+      </c>
+      <c r="T194" s="9">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="U194" s="9">
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="V194" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="W194" s="9">
+        <v>0</v>
+      </c>
+      <c r="X194" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="Y194" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z194" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA194" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB194" s="9">
+        <v>0.13636363636363635</v>
+      </c>
+      <c r="AC194" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD194" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE194" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF194" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG194" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH194" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI194" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ194" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK194" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL194" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM194" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN194" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO194" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP194" s="4">
         <v>58</v>
       </c>
@@ -28888,7 +30790,7 @@
         <v>19951</v>
       </c>
       <c r="B199" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C199" s="4">
         <v>51</v>
@@ -28918,35 +30820,93 @@
         <v>58</v>
       </c>
       <c r="L199" s="4"/>
-      <c r="M199" s="5"/>
-      <c r="N199" s="6"/>
-      <c r="O199" s="6"/>
-      <c r="P199" s="7"/>
-      <c r="Q199" s="8"/>
-      <c r="R199" s="8"/>
-      <c r="S199" s="8"/>
-      <c r="T199" s="9"/>
-      <c r="U199" s="9"/>
-      <c r="V199" s="9"/>
-      <c r="W199" s="9"/>
-      <c r="X199" s="9"/>
-      <c r="Y199" s="9"/>
-      <c r="Z199" s="9"/>
-      <c r="AA199" s="9"/>
-      <c r="AB199" s="9"/>
-      <c r="AC199" s="9"/>
-      <c r="AD199" s="6"/>
-      <c r="AE199" s="6"/>
-      <c r="AF199" s="6"/>
-      <c r="AG199" s="6"/>
-      <c r="AH199" s="6"/>
-      <c r="AI199" s="6"/>
-      <c r="AJ199" s="6"/>
-      <c r="AK199" s="6"/>
-      <c r="AL199" s="6"/>
-      <c r="AM199" s="6"/>
-      <c r="AN199" s="9"/>
-      <c r="AO199" s="6"/>
+      <c r="M199" s="5">
+        <v>9136.9300000000003</v>
+      </c>
+      <c r="N199" s="6">
+        <v>98</v>
+      </c>
+      <c r="O199" s="6">
+        <v>61</v>
+      </c>
+      <c r="P199" s="7">
+        <v>17.03230206185567</v>
+      </c>
+      <c r="Q199" s="8">
+        <v>41.224590163934423</v>
+      </c>
+      <c r="R199" s="8">
+        <v>13.074044262295082</v>
+      </c>
+      <c r="S199" s="8">
+        <v>7</v>
+      </c>
+      <c r="T199" s="9">
+        <v>0.098360655737704916</v>
+      </c>
+      <c r="U199" s="9">
+        <v>0.11475409836065574</v>
+      </c>
+      <c r="V199" s="9">
+        <v>0</v>
+      </c>
+      <c r="W199" s="9">
+        <v>0</v>
+      </c>
+      <c r="X199" s="9">
+        <v>0.016393442622950821</v>
+      </c>
+      <c r="Y199" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z199" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA199" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB199" s="9">
+        <v>0.016393442622950821</v>
+      </c>
+      <c r="AC199" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD199" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE199" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH199" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL199" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN199" s="9">
+        <v>0.081967213114754092</v>
+      </c>
+      <c r="AO199" s="6">
+        <v>5</v>
+      </c>
       <c t="s" r="AP199" s="4">
         <v>58</v>
       </c>
@@ -28987,7 +30947,7 @@
         <v>19954</v>
       </c>
       <c r="B200" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C200" s="4">
         <v>51</v>
@@ -29017,35 +30977,93 @@
         <v>58</v>
       </c>
       <c r="L200" s="4"/>
-      <c r="M200" s="5"/>
-      <c r="N200" s="6"/>
-      <c r="O200" s="6"/>
-      <c r="P200" s="7"/>
-      <c r="Q200" s="8"/>
-      <c r="R200" s="8"/>
-      <c r="S200" s="8"/>
-      <c r="T200" s="9"/>
-      <c r="U200" s="9"/>
-      <c r="V200" s="9"/>
-      <c r="W200" s="9"/>
-      <c r="X200" s="9"/>
-      <c r="Y200" s="9"/>
-      <c r="Z200" s="9"/>
-      <c r="AA200" s="9"/>
-      <c r="AB200" s="9"/>
-      <c r="AC200" s="9"/>
-      <c r="AD200" s="6"/>
-      <c r="AE200" s="6"/>
-      <c r="AF200" s="6"/>
-      <c r="AG200" s="6"/>
-      <c r="AH200" s="6"/>
-      <c r="AI200" s="6"/>
-      <c r="AJ200" s="6"/>
-      <c r="AK200" s="6"/>
-      <c r="AL200" s="6"/>
-      <c r="AM200" s="6"/>
-      <c r="AN200" s="9"/>
-      <c r="AO200" s="6"/>
+      <c r="M200" s="5">
+        <v>3025.0999999999999</v>
+      </c>
+      <c r="N200" s="6">
+        <v>40</v>
+      </c>
+      <c r="O200" s="6">
+        <v>20</v>
+      </c>
+      <c r="P200" s="7">
+        <v>9.8567452380952378</v>
+      </c>
+      <c r="Q200" s="8">
+        <v>24.016665</v>
+      </c>
+      <c r="R200" s="8">
+        <v>6.8166650000000004</v>
+      </c>
+      <c r="S200" s="8">
+        <v>7</v>
+      </c>
+      <c r="T200" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="U200" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="V200" s="9">
+        <v>0</v>
+      </c>
+      <c r="W200" s="9">
+        <v>0</v>
+      </c>
+      <c r="X200" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="Y200" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD200" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE200" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH200" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO200" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP200" s="4">
         <v>58</v>
       </c>
@@ -29755,7 +31773,7 @@
         <v>19961</v>
       </c>
       <c r="B206" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C206" s="4">
         <v>51</v>
@@ -29785,35 +31803,93 @@
         <v>58</v>
       </c>
       <c r="L206" s="4"/>
-      <c r="M206" s="5"/>
-      <c r="N206" s="6"/>
-      <c r="O206" s="6"/>
-      <c r="P206" s="7"/>
-      <c r="Q206" s="8"/>
-      <c r="R206" s="8"/>
-      <c r="S206" s="8"/>
-      <c r="T206" s="9"/>
-      <c r="U206" s="9"/>
-      <c r="V206" s="9"/>
-      <c r="W206" s="9"/>
-      <c r="X206" s="9"/>
-      <c r="Y206" s="9"/>
-      <c r="Z206" s="9"/>
-      <c r="AA206" s="9"/>
-      <c r="AB206" s="9"/>
-      <c r="AC206" s="9"/>
-      <c r="AD206" s="6"/>
-      <c r="AE206" s="6"/>
-      <c r="AF206" s="6"/>
-      <c r="AG206" s="6"/>
-      <c r="AH206" s="6"/>
-      <c r="AI206" s="6"/>
-      <c r="AJ206" s="6"/>
-      <c r="AK206" s="6"/>
-      <c r="AL206" s="6"/>
-      <c r="AM206" s="6"/>
-      <c r="AN206" s="9"/>
-      <c r="AO206" s="6"/>
+      <c r="M206" s="5">
+        <v>3265.5999999999999</v>
+      </c>
+      <c r="N206" s="6">
+        <v>36</v>
+      </c>
+      <c r="O206" s="6">
+        <v>13</v>
+      </c>
+      <c r="P206" s="7">
+        <v>5.5828694444444444</v>
+      </c>
+      <c r="Q206" s="8">
+        <v>20.265384615384615</v>
+      </c>
+      <c r="R206" s="8">
+        <v>7.8602538461538467</v>
+      </c>
+      <c r="S206" s="8">
+        <v>7</v>
+      </c>
+      <c r="T206" s="9">
+        <v>0.38461538461538464</v>
+      </c>
+      <c r="U206" s="9">
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="V206" s="9">
+        <v>0</v>
+      </c>
+      <c r="W206" s="9">
+        <v>0</v>
+      </c>
+      <c r="X206" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y206" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z206" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA206" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB206" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC206" s="9">
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="AD206" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE206" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM206" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN206" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO206" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP206" s="4">
         <v>58</v>
       </c>
@@ -29854,7 +31930,7 @@
         <v>19962</v>
       </c>
       <c r="B207" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C207" s="4">
         <v>51</v>
@@ -29884,35 +31960,93 @@
         <v>58</v>
       </c>
       <c r="L207" s="4"/>
-      <c r="M207" s="5"/>
-      <c r="N207" s="6"/>
-      <c r="O207" s="6"/>
-      <c r="P207" s="7"/>
-      <c r="Q207" s="8"/>
-      <c r="R207" s="8"/>
-      <c r="S207" s="8"/>
-      <c r="T207" s="9"/>
-      <c r="U207" s="9"/>
-      <c r="V207" s="9"/>
-      <c r="W207" s="9"/>
-      <c r="X207" s="9"/>
-      <c r="Y207" s="9"/>
-      <c r="Z207" s="9"/>
-      <c r="AA207" s="9"/>
-      <c r="AB207" s="9"/>
-      <c r="AC207" s="9"/>
-      <c r="AD207" s="6"/>
-      <c r="AE207" s="6"/>
-      <c r="AF207" s="6"/>
-      <c r="AG207" s="6"/>
-      <c r="AH207" s="6"/>
-      <c r="AI207" s="6"/>
-      <c r="AJ207" s="6"/>
-      <c r="AK207" s="6"/>
-      <c r="AL207" s="6"/>
-      <c r="AM207" s="6"/>
-      <c r="AN207" s="9"/>
-      <c r="AO207" s="6"/>
+      <c r="M207" s="5">
+        <v>0</v>
+      </c>
+      <c r="N207" s="6">
+        <v>48</v>
+      </c>
+      <c r="O207" s="6">
+        <v>19</v>
+      </c>
+      <c r="P207" s="7">
+        <v>11.812319565217392</v>
+      </c>
+      <c r="Q207" s="8">
+        <v>33.578068421052627</v>
+      </c>
+      <c r="R207" s="8">
+        <v>15.511405263157895</v>
+      </c>
+      <c r="S207" s="8">
+        <v>7</v>
+      </c>
+      <c r="T207" s="9">
+        <v>0</v>
+      </c>
+      <c r="U207" s="9">
+        <v>0.10526315789473684</v>
+      </c>
+      <c r="V207" s="9">
+        <v>0</v>
+      </c>
+      <c r="W207" s="9">
+        <v>0</v>
+      </c>
+      <c r="X207" s="9">
+        <v>0.10526315789473684</v>
+      </c>
+      <c r="Y207" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD207" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE207" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH207" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO207" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP207" s="4">
         <v>58</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-27).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-27).xlsx
@@ -935,34 +935,34 @@
     <t>214</t>
   </si>
   <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>R$ 9.451,70</t>
-  </si>
-  <si>
-    <t>101.1</t>
-  </si>
-  <si>
-    <t>66.0</t>
-  </si>
-  <si>
-    <t>7.46</t>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 9.386,45</t>
+  </si>
+  <si>
+    <t>100.5</t>
+  </si>
+  <si>
+    <t>65.9</t>
+  </si>
+  <si>
+    <t>7.40</t>
   </si>
   <si>
     <t>22.9</t>
   </si>
   <si>
-    <t>8.7</t>
-  </si>
-  <si>
-    <t>6.0</t>
+    <t>8.8</t>
+  </si>
+  <si>
+    <t>6.1</t>
   </si>
   <si>
     <t>29.5%</t>
   </si>
   <si>
-    <t>17.8%</t>
+    <t>17.6%</t>
   </si>
   <si>
     <t>1.3%</t>
@@ -971,7 +971,7 @@
     <t>0.4%</t>
   </si>
   <si>
-    <t>3.0%</t>
+    <t>3.1%</t>
   </si>
   <si>
     <t>0.9%</t>
@@ -986,34 +986,34 @@
     <t>2.8%</t>
   </si>
   <si>
-    <t>6.3%</t>
-  </si>
-  <si>
-    <t>2448.0</t>
-  </si>
-  <si>
-    <t>2073.0</t>
-  </si>
-  <si>
-    <t>148.0</t>
+    <t>6.2%</t>
+  </si>
+  <si>
+    <t>2480.0</t>
+  </si>
+  <si>
+    <t>2098.0</t>
+  </si>
+  <si>
+    <t>151.0</t>
   </si>
   <si>
     <t>42.0</t>
   </si>
   <si>
-    <t>356.0</t>
-  </si>
-  <si>
-    <t>103.0</t>
+    <t>370.0</t>
+  </si>
+  <si>
+    <t>105.0</t>
   </si>
   <si>
     <t>15.0</t>
   </si>
   <si>
-    <t>678.0</t>
-  </si>
-  <si>
-    <t>325.0</t>
+    <t>687.0</t>
+  </si>
+  <si>
+    <t>329.0</t>
   </si>
   <si>
     <t>740.0</t>
@@ -6731,7 +6731,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6761,35 +6761,93 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
-      <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
-      <c r="U36" s="9"/>
-      <c r="V36" s="9"/>
-      <c r="W36" s="9"/>
-      <c r="X36" s="9"/>
-      <c r="Y36" s="9"/>
-      <c r="Z36" s="9"/>
-      <c r="AA36" s="9"/>
-      <c r="AB36" s="9"/>
-      <c r="AC36" s="9"/>
-      <c r="AD36" s="6"/>
-      <c r="AE36" s="6"/>
-      <c r="AF36" s="6"/>
-      <c r="AG36" s="6"/>
-      <c r="AH36" s="6"/>
-      <c r="AI36" s="6"/>
-      <c r="AJ36" s="6"/>
-      <c r="AK36" s="6"/>
-      <c r="AL36" s="6"/>
-      <c r="AM36" s="6"/>
-      <c r="AN36" s="9"/>
-      <c r="AO36" s="6"/>
+      <c r="M36" s="5">
+        <v>6850.7200000000003</v>
+      </c>
+      <c r="N36" s="6">
+        <v>89</v>
+      </c>
+      <c r="O36" s="6">
+        <v>79</v>
+      </c>
+      <c r="P36" s="7">
+        <v>4.7196965909090913</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>23.021518987341771</v>
+      </c>
+      <c r="R36" s="8">
+        <v>11.923246052631578</v>
+      </c>
+      <c r="S36" s="8">
+        <v>7</v>
+      </c>
+      <c r="T36" s="9">
+        <v>0.379746835443038</v>
+      </c>
+      <c r="U36" s="9">
+        <v>0.15189873417721519</v>
+      </c>
+      <c r="V36" s="9">
+        <v>0</v>
+      </c>
+      <c r="W36" s="9">
+        <v>0</v>
+      </c>
+      <c r="X36" s="9">
+        <v>0.11392405063291139</v>
+      </c>
+      <c r="Y36" s="9">
+        <v>0.012658227848101266</v>
+      </c>
+      <c r="Z36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="9">
+        <v>0.050632911392405063</v>
+      </c>
+      <c r="AB36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="6">
+        <v>14</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>12</v>
+      </c>
+      <c r="AF36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="6">
+        <v>9</v>
+      </c>
+      <c r="AI36" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO36" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP36" s="4">
         <v>58</v>
       </c>
@@ -7613,7 +7671,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>51</v>
@@ -7643,35 +7701,93 @@
         <v>58</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="6"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
-      <c r="T42" s="9"/>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="6"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="6"/>
-      <c r="AL42" s="6"/>
-      <c r="AM42" s="6"/>
-      <c r="AN42" s="9"/>
-      <c r="AO42" s="6"/>
+      <c r="M42" s="5">
+        <v>7347.4399999999996</v>
+      </c>
+      <c r="N42" s="6">
+        <v>80</v>
+      </c>
+      <c r="O42" s="6">
+        <v>60</v>
+      </c>
+      <c r="P42" s="7">
+        <v>6.0517089743589745</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>22.573611666666668</v>
+      </c>
+      <c r="R42" s="8">
+        <v>9.3375711864406785</v>
+      </c>
+      <c r="S42" s="8">
+        <v>7</v>
+      </c>
+      <c r="T42" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="U42" s="9">
+        <v>0.016666666666666666</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0</v>
+      </c>
+      <c r="W42" s="9">
+        <v>0</v>
+      </c>
+      <c r="X42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="9">
+        <v>0.016666666666666666</v>
+      </c>
+      <c r="AB42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP42" s="4">
         <v>58</v>
       </c>
@@ -8962,7 +9078,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -8992,35 +9108,93 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
-      <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
-      <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
-      <c r="U51" s="9"/>
-      <c r="V51" s="9"/>
-      <c r="W51" s="9"/>
-      <c r="X51" s="9"/>
-      <c r="Y51" s="9"/>
-      <c r="Z51" s="9"/>
-      <c r="AA51" s="9"/>
-      <c r="AB51" s="9"/>
-      <c r="AC51" s="9"/>
-      <c r="AD51" s="6"/>
-      <c r="AE51" s="6"/>
-      <c r="AF51" s="6"/>
-      <c r="AG51" s="6"/>
-      <c r="AH51" s="6"/>
-      <c r="AI51" s="6"/>
-      <c r="AJ51" s="6"/>
-      <c r="AK51" s="6"/>
-      <c r="AL51" s="6"/>
-      <c r="AM51" s="6"/>
-      <c r="AN51" s="9"/>
-      <c r="AO51" s="6"/>
+      <c r="M51" s="5">
+        <v>1213.48</v>
+      </c>
+      <c r="N51" s="6">
+        <v>11</v>
+      </c>
+      <c r="O51" s="6">
+        <v>8</v>
+      </c>
+      <c r="P51" s="7">
+        <v>1.8500000000000001</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>8.7145875000000004</v>
+      </c>
+      <c r="R51" s="8">
+        <v>1.0805499999999999</v>
+      </c>
+      <c r="S51" s="8">
+        <v>7</v>
+      </c>
+      <c r="T51" s="9">
+        <v>1</v>
+      </c>
+      <c r="U51" s="9">
+        <v>0.875</v>
+      </c>
+      <c r="V51" s="9">
+        <v>0</v>
+      </c>
+      <c r="W51" s="9">
+        <v>0</v>
+      </c>
+      <c r="X51" s="9">
+        <v>0.375</v>
+      </c>
+      <c r="Y51" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="Z51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AB51" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AC51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD51" s="6">
+        <v>12</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI51" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL51" s="6">
+        <v>4</v>
+      </c>
+      <c r="AM51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP51" s="4">
         <v>58</v>
       </c>
@@ -10031,33 +10205,79 @@
       <c r="L58" s="4"/>
       <c r="M58" s="5"/>
       <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
+      <c r="O58" s="6">
+        <v>100</v>
+      </c>
       <c r="P58" s="7"/>
       <c r="Q58" s="8"/>
       <c r="R58" s="8"/>
-      <c r="S58" s="8"/>
+      <c r="S58" s="8">
+        <v>7</v>
+      </c>
       <c r="T58" s="9"/>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-      <c r="AA58" s="9"/>
-      <c r="AB58" s="9"/>
-      <c r="AC58" s="9"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="6"/>
-      <c r="AM58" s="6"/>
-      <c r="AN58" s="9"/>
-      <c r="AO58" s="6"/>
+      <c r="U58" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="V58" s="9">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0</v>
+      </c>
+      <c r="X58" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="Y58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>3</v>
+      </c>
+      <c r="AG58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP58" s="4">
         <v>58</v>
       </c>
@@ -16411,7 +16631,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>51</v>
@@ -16441,14 +16661,26 @@
         <v>58</v>
       </c>
       <c r="L102" s="4"/>
-      <c r="M102" s="5"/>
-      <c r="N102" s="6"/>
+      <c r="M102" s="5">
+        <v>8059.6300000000001</v>
+      </c>
+      <c r="N102" s="6">
+        <v>87</v>
+      </c>
       <c r="O102" s="6"/>
-      <c r="P102" s="7"/>
-      <c r="Q102" s="8"/>
-      <c r="R102" s="8"/>
+      <c r="P102" s="7">
+        <v>9.7945079545454536</v>
+      </c>
+      <c r="Q102" s="8">
+        <v>38.990303636363635</v>
+      </c>
+      <c r="R102" s="8">
+        <v>41.501307843137255</v>
+      </c>
       <c r="S102" s="8"/>
-      <c r="T102" s="9"/>
+      <c r="T102" s="9">
+        <v>0.18181818181818182</v>
+      </c>
       <c r="U102" s="9"/>
       <c r="V102" s="9"/>
       <c r="W102" s="9"/>
@@ -30220,7 +30452,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>51</v>
@@ -30250,14 +30482,26 @@
         <v>58</v>
       </c>
       <c r="L195" s="4"/>
-      <c r="M195" s="5"/>
-      <c r="N195" s="6"/>
+      <c r="M195" s="5">
+        <v>11911.48</v>
+      </c>
+      <c r="N195" s="6">
+        <v>131</v>
+      </c>
       <c r="O195" s="6"/>
-      <c r="P195" s="7"/>
-      <c r="Q195" s="8"/>
-      <c r="R195" s="8"/>
+      <c r="P195" s="7">
+        <v>4.5380574803149605</v>
+      </c>
+      <c r="Q195" s="8">
+        <v>19.452355434782611</v>
+      </c>
+      <c r="R195" s="8">
+        <v>8.096519780219781</v>
+      </c>
       <c r="S195" s="8"/>
-      <c r="T195" s="9"/>
+      <c r="T195" s="9">
+        <v>0.19565217391304349</v>
+      </c>
       <c r="U195" s="9"/>
       <c r="V195" s="9"/>
       <c r="W195" s="9"/>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-27).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-27).xlsx
@@ -935,16 +935,16 @@
     <t>214</t>
   </si>
   <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>R$ 9.386,45</t>
-  </si>
-  <si>
-    <t>100.5</t>
-  </si>
-  <si>
-    <t>65.9</t>
+    <t>26</t>
+  </si>
+  <si>
+    <t>R$ 9.412,17</t>
+  </si>
+  <si>
+    <t>100.6</t>
+  </si>
+  <si>
+    <t>66.3</t>
   </si>
   <si>
     <t>7.40</t>
@@ -956,22 +956,22 @@
     <t>8.8</t>
   </si>
   <si>
-    <t>6.1</t>
-  </si>
-  <si>
-    <t>29.5%</t>
-  </si>
-  <si>
-    <t>17.6%</t>
-  </si>
-  <si>
-    <t>1.3%</t>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>29.2%</t>
+  </si>
+  <si>
+    <t>17.4%</t>
+  </si>
+  <si>
+    <t>1.2%</t>
   </si>
   <si>
     <t>0.4%</t>
   </si>
   <si>
-    <t>3.1%</t>
+    <t>3.0%</t>
   </si>
   <si>
     <t>0.9%</t>
@@ -983,22 +983,22 @@
     <t>5.8%</t>
   </si>
   <si>
-    <t>2.8%</t>
+    <t>2.7%</t>
   </si>
   <si>
     <t>6.2%</t>
   </si>
   <si>
-    <t>2480.0</t>
-  </si>
-  <si>
-    <t>2098.0</t>
-  </si>
-  <si>
-    <t>151.0</t>
-  </si>
-  <si>
-    <t>42.0</t>
+    <t>2519.0</t>
+  </si>
+  <si>
+    <t>2135.0</t>
+  </si>
+  <si>
+    <t>152.0</t>
+  </si>
+  <si>
+    <t>43.0</t>
   </si>
   <si>
     <t>370.0</t>
@@ -1007,16 +1007,16 @@
     <t>105.0</t>
   </si>
   <si>
-    <t>15.0</t>
-  </si>
-  <si>
-    <t>687.0</t>
-  </si>
-  <si>
-    <t>329.0</t>
-  </si>
-  <si>
-    <t>740.0</t>
+    <t>16.0</t>
+  </si>
+  <si>
+    <t>705.0</t>
+  </si>
+  <si>
+    <t>334.0</t>
+  </si>
+  <si>
+    <t>754.0</t>
   </si>
   <si>
     <t>0.7%</t>
@@ -2209,7 +2209,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>51</v>
@@ -2239,35 +2239,93 @@
         <v>58</v>
       </c>
       <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
-      <c r="AC6" s="9"/>
-      <c r="AD6" s="6"/>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-      <c r="AG6" s="6"/>
-      <c r="AH6" s="6"/>
-      <c r="AI6" s="6"/>
-      <c r="AJ6" s="6"/>
-      <c r="AK6" s="6"/>
-      <c r="AL6" s="6"/>
-      <c r="AM6" s="6"/>
-      <c r="AN6" s="9"/>
-      <c r="AO6" s="6"/>
+      <c r="M6" s="5">
+        <v>17227.669999999998</v>
+      </c>
+      <c r="N6" s="6">
+        <v>167</v>
+      </c>
+      <c r="O6" s="6">
+        <v>128</v>
+      </c>
+      <c r="P6" s="7">
+        <v>7.2276769696969705</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>17.619921874999999</v>
+      </c>
+      <c r="R6" s="8">
+        <v>3.4194663999999997</v>
+      </c>
+      <c r="S6" s="8">
+        <v>7</v>
+      </c>
+      <c r="T6" s="9">
+        <v>0.390625</v>
+      </c>
+      <c r="U6" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="V6" s="9">
+        <v>0</v>
+      </c>
+      <c r="W6" s="9">
+        <v>0</v>
+      </c>
+      <c r="X6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="9">
+        <v>0.0078125</v>
+      </c>
+      <c r="AA6" s="9">
+        <v>0.0390625</v>
+      </c>
+      <c r="AB6" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="AC6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>10</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>8</v>
+      </c>
+      <c r="AF6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK6" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL6" s="6">
+        <v>4</v>
+      </c>
+      <c r="AM6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP6" s="4">
         <v>58</v>
       </c>
@@ -7092,7 +7150,7 @@
         <v>11.300000000000001</v>
       </c>
       <c r="S38" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T38" s="9">
         <v>0.14736842105263157</v>
@@ -16667,7 +16725,9 @@
       <c r="N102" s="6">
         <v>87</v>
       </c>
-      <c r="O102" s="6"/>
+      <c r="O102" s="6">
+        <v>62</v>
+      </c>
       <c r="P102" s="7">
         <v>9.7945079545454536</v>
       </c>
@@ -16677,31 +16737,75 @@
       <c r="R102" s="8">
         <v>41.501307843137255</v>
       </c>
-      <c r="S102" s="8"/>
+      <c r="S102" s="8">
+        <v>7</v>
+      </c>
       <c r="T102" s="9">
         <v>0.18181818181818182</v>
       </c>
-      <c r="U102" s="9"/>
-      <c r="V102" s="9"/>
-      <c r="W102" s="9"/>
-      <c r="X102" s="9"/>
-      <c r="Y102" s="9"/>
-      <c r="Z102" s="9"/>
-      <c r="AA102" s="9"/>
-      <c r="AB102" s="9"/>
-      <c r="AC102" s="9"/>
-      <c r="AD102" s="6"/>
-      <c r="AE102" s="6"/>
-      <c r="AF102" s="6"/>
-      <c r="AG102" s="6"/>
-      <c r="AH102" s="6"/>
-      <c r="AI102" s="6"/>
-      <c r="AJ102" s="6"/>
-      <c r="AK102" s="6"/>
-      <c r="AL102" s="6"/>
-      <c r="AM102" s="6"/>
-      <c r="AN102" s="9"/>
-      <c r="AO102" s="6"/>
+      <c r="U102" s="9">
+        <v>0.43548387096774194</v>
+      </c>
+      <c r="V102" s="9">
+        <v>0</v>
+      </c>
+      <c r="W102" s="9">
+        <v>0</v>
+      </c>
+      <c r="X102" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="9">
+        <v>0.19354838709677419</v>
+      </c>
+      <c r="AB102" s="9">
+        <v>0.016129032258064516</v>
+      </c>
+      <c r="AC102" s="9">
+        <v>0.22580645161290322</v>
+      </c>
+      <c r="AD102" s="6">
+        <v>27</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>27</v>
+      </c>
+      <c r="AF102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="6">
+        <v>12</v>
+      </c>
+      <c r="AL102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM102" s="6">
+        <v>14</v>
+      </c>
+      <c r="AN102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP102" s="4">
         <v>58</v>
       </c>
@@ -24885,7 +24989,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>51</v>
@@ -24915,35 +25019,93 @@
         <v>58</v>
       </c>
       <c r="L158" s="4"/>
-      <c r="M158" s="5"/>
-      <c r="N158" s="6"/>
-      <c r="O158" s="6"/>
-      <c r="P158" s="7"/>
-      <c r="Q158" s="8"/>
-      <c r="R158" s="8"/>
-      <c r="S158" s="8"/>
-      <c r="T158" s="9"/>
-      <c r="U158" s="9"/>
-      <c r="V158" s="9"/>
-      <c r="W158" s="9"/>
-      <c r="X158" s="9"/>
-      <c r="Y158" s="9"/>
-      <c r="Z158" s="9"/>
-      <c r="AA158" s="9"/>
-      <c r="AB158" s="9"/>
-      <c r="AC158" s="9"/>
-      <c r="AD158" s="6"/>
-      <c r="AE158" s="6"/>
-      <c r="AF158" s="6"/>
-      <c r="AG158" s="6"/>
-      <c r="AH158" s="6"/>
-      <c r="AI158" s="6"/>
-      <c r="AJ158" s="6"/>
-      <c r="AK158" s="6"/>
-      <c r="AL158" s="6"/>
-      <c r="AM158" s="6"/>
-      <c r="AN158" s="9"/>
-      <c r="AO158" s="6"/>
+      <c r="M158" s="5">
+        <v>6278.4499999999998</v>
+      </c>
+      <c r="N158" s="6">
+        <v>55</v>
+      </c>
+      <c r="O158" s="6">
+        <v>50</v>
+      </c>
+      <c r="P158" s="7">
+        <v>7.2002982142857146</v>
+      </c>
+      <c r="Q158" s="8">
+        <v>27.006665999999999</v>
+      </c>
+      <c r="R158" s="8">
+        <v>12.595334000000001</v>
+      </c>
+      <c r="S158" s="8">
+        <v>7</v>
+      </c>
+      <c r="T158" s="9">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="U158" s="9">
+        <v>0</v>
+      </c>
+      <c r="V158" s="9">
+        <v>0</v>
+      </c>
+      <c r="W158" s="9">
+        <v>0</v>
+      </c>
+      <c r="X158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO158" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP158" s="4">
         <v>58</v>
       </c>
@@ -30488,7 +30650,9 @@
       <c r="N195" s="6">
         <v>131</v>
       </c>
-      <c r="O195" s="6"/>
+      <c r="O195" s="6">
+        <v>92</v>
+      </c>
       <c r="P195" s="7">
         <v>4.5380574803149605</v>
       </c>
@@ -30498,31 +30662,75 @@
       <c r="R195" s="8">
         <v>8.096519780219781</v>
       </c>
-      <c r="S195" s="8"/>
+      <c r="S195" s="8">
+        <v>7</v>
+      </c>
       <c r="T195" s="9">
         <v>0.19565217391304349</v>
       </c>
-      <c r="U195" s="9"/>
-      <c r="V195" s="9"/>
-      <c r="W195" s="9"/>
-      <c r="X195" s="9"/>
-      <c r="Y195" s="9"/>
-      <c r="Z195" s="9"/>
-      <c r="AA195" s="9"/>
-      <c r="AB195" s="9"/>
-      <c r="AC195" s="9"/>
-      <c r="AD195" s="6"/>
-      <c r="AE195" s="6"/>
-      <c r="AF195" s="6"/>
-      <c r="AG195" s="6"/>
-      <c r="AH195" s="6"/>
-      <c r="AI195" s="6"/>
-      <c r="AJ195" s="6"/>
-      <c r="AK195" s="6"/>
-      <c r="AL195" s="6"/>
-      <c r="AM195" s="6"/>
-      <c r="AN195" s="9"/>
-      <c r="AO195" s="6"/>
+      <c r="U195" s="9">
+        <v>0.021739130434782608</v>
+      </c>
+      <c r="V195" s="9">
+        <v>0.010869565217391304</v>
+      </c>
+      <c r="W195" s="9">
+        <v>0.010869565217000001</v>
+      </c>
+      <c r="X195" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y195" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA195" s="9">
+        <v>0.010869565217391304</v>
+      </c>
+      <c r="AB195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD195" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE195" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF195" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG195" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK195" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO195" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP195" s="4">
         <v>58</v>
       </c>
